--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="200">
   <si>
     <t>TileID</t>
   </si>
@@ -109,51 +109,6 @@
     <t>Union County</t>
   </si>
   <si>
-    <t>Bloom Township (Fairfield)</t>
-  </si>
-  <si>
-    <t>Violet Township (Fairfield)</t>
-  </si>
-  <si>
-    <t>Blendon Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Brown Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Clinton Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Franklin Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Jackson Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Jefferson Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Madison Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Mifflin Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Perry Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Prairie Township (Franklin)</t>
-  </si>
-  <si>
-    <t>Etna Township (Licking)</t>
-  </si>
-  <si>
-    <t>Granville Township (Licking)</t>
-  </si>
-  <si>
-    <t>Jerome Township (Union)</t>
-  </si>
-  <si>
     <t>Ashville</t>
   </si>
   <si>
@@ -337,51 +292,6 @@
     <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0500000US39159.svg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390450695099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390458020699999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390490692299999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390490944299999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390491611299999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390492828099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390493777299999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390493861299999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390494641099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390495006499999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390496184099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390496457099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390892569099999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US390893141699999.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/0700000US391593904699999.svg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/1600000US3902680.svg</t>
   </si>
   <si>
@@ -569,51 +479,6 @@
   </si>
   <si>
     <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0500000US39159</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390450695099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390458020699999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390490692299999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390490944299999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390491611299999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390492828099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390493777299999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390493861299999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390494641099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390495006499999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390496184099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390496457099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390892569099999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US390893141699999</t>
-  </si>
-  <si>
-    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=0700000US391593904699999</t>
   </si>
   <si>
     <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=1600000US3902680</t>
@@ -1119,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1171,25 +1036,25 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J2" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K2" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1200,25 +1065,25 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1229,25 +1094,25 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J4" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1258,25 +1123,25 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J5" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K5" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1287,25 +1152,25 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J6" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K6" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1316,25 +1181,25 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K7" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1345,25 +1210,25 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J8" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K8" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1374,25 +1239,25 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J9" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1403,25 +1268,25 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J10" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K10" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1432,25 +1297,25 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J11" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1461,25 +1326,25 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K12" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1490,25 +1355,25 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J13" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1519,25 +1384,25 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K14" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1548,25 +1413,25 @@
         <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J15" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K15" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1577,25 +1442,25 @@
         <v>30</v>
       </c>
       <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="I16" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J16" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K16" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="3:13">
@@ -1606,25 +1471,25 @@
         <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J17" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="3:13">
@@ -1635,25 +1500,25 @@
         <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J18" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K18" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="3:13">
@@ -1664,25 +1529,25 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J19" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K19" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="3:13">
@@ -1693,25 +1558,25 @@
         <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K20" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="3:13">
@@ -1722,25 +1587,25 @@
         <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J21" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K21" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="3:13">
@@ -1751,25 +1616,25 @@
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="I22" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="3:13">
@@ -1780,25 +1645,25 @@
         <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I23" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J23" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K23" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="3:13">
@@ -1809,25 +1674,25 @@
         <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I24" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J24" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K24" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="3:13">
@@ -1838,25 +1703,25 @@
         <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J25" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K25" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="3:13">
@@ -1867,25 +1732,25 @@
         <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="I26" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J26" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="3:13">
@@ -1896,25 +1761,25 @@
         <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I27" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J27" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K27" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="3:13">
@@ -1925,25 +1790,25 @@
         <v>42</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="I28" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J28" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K28" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="3:13">
@@ -1954,25 +1819,25 @@
         <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I29" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" t="s">
+        <v>138</v>
+      </c>
+      <c r="K29" t="s">
+        <v>139</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="J29" t="s">
-        <v>168</v>
-      </c>
-      <c r="K29" t="s">
-        <v>169</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="30" spans="3:13">
@@ -1983,25 +1848,25 @@
         <v>44</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J30" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="K30" t="s">
-        <v>169</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="31" spans="3:13">
@@ -2012,25 +1877,25 @@
         <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="I31" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J31" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="32" spans="3:13">
@@ -2041,25 +1906,25 @@
         <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="I32" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J32" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K32" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="3:13">
@@ -2070,25 +1935,25 @@
         <v>47</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="I33" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J33" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K33" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="3:13">
@@ -2099,25 +1964,25 @@
         <v>48</v>
       </c>
       <c r="F34" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="I34" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J34" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K34" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="3:13">
@@ -2128,25 +1993,25 @@
         <v>49</v>
       </c>
       <c r="F35" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J35" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K35" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="3:13">
@@ -2157,25 +2022,25 @@
         <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I36" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J36" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K36" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="3:13">
@@ -2186,25 +2051,25 @@
         <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I37" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K37" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="3:13">
@@ -2215,25 +2080,25 @@
         <v>52</v>
       </c>
       <c r="F38" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I38" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K38" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="3:13">
@@ -2244,25 +2109,25 @@
         <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="I39" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J39" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K39" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="3:13">
@@ -2273,25 +2138,25 @@
         <v>54</v>
       </c>
       <c r="F40" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="I40" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J40" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K40" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="3:13">
@@ -2302,25 +2167,25 @@
         <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="I41" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J41" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K41" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="3:13">
@@ -2331,25 +2196,25 @@
         <v>56</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="I42" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J42" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K42" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="3:13">
@@ -2360,25 +2225,25 @@
         <v>57</v>
       </c>
       <c r="F43" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I43" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J43" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K43" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="3:13">
@@ -2389,25 +2254,25 @@
         <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="I44" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J44" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K44" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="3:13">
@@ -2418,25 +2283,25 @@
         <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I45" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J45" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K45" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="3:13">
@@ -2447,25 +2312,25 @@
         <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="I46" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J46" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K46" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="3:13">
@@ -2476,25 +2341,25 @@
         <v>61</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="I47" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J47" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K47" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="3:13">
@@ -2505,25 +2370,25 @@
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="I48" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J48" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K48" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="3:13">
@@ -2534,25 +2399,25 @@
         <v>63</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="I49" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J49" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K49" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="3:13">
@@ -2563,25 +2428,25 @@
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I50" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J50" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K50" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="3:13">
@@ -2592,25 +2457,25 @@
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I51" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J51" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K51" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="3:13">
@@ -2621,25 +2486,25 @@
         <v>66</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="I52" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J52" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K52" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="3:13">
@@ -2650,25 +2515,25 @@
         <v>67</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="I53" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J53" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K53" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="3:13">
@@ -2679,25 +2544,25 @@
         <v>68</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="I54" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J54" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K54" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="3:13">
@@ -2708,25 +2573,25 @@
         <v>69</v>
       </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="I55" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J55" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K55" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="3:13">
@@ -2737,25 +2602,25 @@
         <v>70</v>
       </c>
       <c r="F56" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I56" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J56" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K56" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="3:13">
@@ -2766,25 +2631,25 @@
         <v>71</v>
       </c>
       <c r="F57" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="I57" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J57" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K57" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="3:13">
@@ -2795,25 +2660,25 @@
         <v>72</v>
       </c>
       <c r="F58" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I58" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J58" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K58" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="3:13">
@@ -2824,25 +2689,25 @@
         <v>73</v>
       </c>
       <c r="F59" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="I59" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J59" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K59" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="3:13">
@@ -2853,489 +2718,54 @@
         <v>74</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="I60" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J60" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K60" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="3:13">
       <c r="C61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
         <v>75</v>
       </c>
       <c r="F61" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="I61" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J61" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="K61" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13">
-      <c r="C62" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" t="s">
-        <v>76</v>
-      </c>
-      <c r="F62" t="s">
-        <v>91</v>
-      </c>
-      <c r="G62" t="s">
-        <v>91</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I62" t="s">
-        <v>167</v>
-      </c>
-      <c r="J62" t="s">
-        <v>168</v>
-      </c>
-      <c r="K62" t="s">
-        <v>169</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13">
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
-        <v>77</v>
-      </c>
-      <c r="F63" t="s">
-        <v>91</v>
-      </c>
-      <c r="G63" t="s">
-        <v>91</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I63" t="s">
-        <v>167</v>
-      </c>
-      <c r="J63" t="s">
-        <v>168</v>
-      </c>
-      <c r="K63" t="s">
-        <v>169</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="64" spans="3:13">
-      <c r="C64" t="s">
-        <v>14</v>
-      </c>
-      <c r="D64" t="s">
-        <v>78</v>
-      </c>
-      <c r="F64" t="s">
-        <v>91</v>
-      </c>
-      <c r="G64" t="s">
-        <v>91</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I64" t="s">
-        <v>167</v>
-      </c>
-      <c r="J64" t="s">
-        <v>168</v>
-      </c>
-      <c r="K64" t="s">
-        <v>169</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="65" spans="3:13">
-      <c r="C65" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" t="s">
-        <v>79</v>
-      </c>
-      <c r="F65" t="s">
-        <v>91</v>
-      </c>
-      <c r="G65" t="s">
-        <v>91</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I65" t="s">
-        <v>167</v>
-      </c>
-      <c r="J65" t="s">
-        <v>168</v>
-      </c>
-      <c r="K65" t="s">
-        <v>169</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="66" spans="3:13">
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>80</v>
-      </c>
-      <c r="F66" t="s">
-        <v>91</v>
-      </c>
-      <c r="G66" t="s">
-        <v>91</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I66" t="s">
-        <v>167</v>
-      </c>
-      <c r="J66" t="s">
-        <v>168</v>
-      </c>
-      <c r="K66" t="s">
-        <v>169</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="67" spans="3:13">
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>81</v>
-      </c>
-      <c r="F67" t="s">
-        <v>91</v>
-      </c>
-      <c r="G67" t="s">
-        <v>91</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I67" t="s">
-        <v>167</v>
-      </c>
-      <c r="J67" t="s">
-        <v>168</v>
-      </c>
-      <c r="K67" t="s">
-        <v>169</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="68" spans="3:13">
-      <c r="C68" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" t="s">
-        <v>82</v>
-      </c>
-      <c r="F68" t="s">
-        <v>91</v>
-      </c>
-      <c r="G68" t="s">
-        <v>91</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I68" t="s">
-        <v>167</v>
-      </c>
-      <c r="J68" t="s">
-        <v>168</v>
-      </c>
-      <c r="K68" t="s">
-        <v>169</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="69" spans="3:13">
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>83</v>
-      </c>
-      <c r="F69" t="s">
-        <v>91</v>
-      </c>
-      <c r="G69" t="s">
-        <v>91</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I69" t="s">
-        <v>167</v>
-      </c>
-      <c r="J69" t="s">
-        <v>168</v>
-      </c>
-      <c r="K69" t="s">
-        <v>169</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="70" spans="3:13">
-      <c r="C70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s">
-        <v>84</v>
-      </c>
-      <c r="F70" t="s">
-        <v>91</v>
-      </c>
-      <c r="G70" t="s">
-        <v>91</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I70" t="s">
-        <v>167</v>
-      </c>
-      <c r="J70" t="s">
-        <v>168</v>
-      </c>
-      <c r="K70" t="s">
-        <v>169</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="71" spans="3:13">
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>85</v>
-      </c>
-      <c r="F71" t="s">
-        <v>91</v>
-      </c>
-      <c r="G71" t="s">
-        <v>91</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I71" t="s">
-        <v>167</v>
-      </c>
-      <c r="J71" t="s">
-        <v>168</v>
-      </c>
-      <c r="K71" t="s">
-        <v>169</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="72" spans="3:13">
-      <c r="C72" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>86</v>
-      </c>
-      <c r="F72" t="s">
-        <v>91</v>
-      </c>
-      <c r="G72" t="s">
-        <v>91</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I72" t="s">
-        <v>167</v>
-      </c>
-      <c r="J72" t="s">
-        <v>168</v>
-      </c>
-      <c r="K72" t="s">
-        <v>169</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="73" spans="3:13">
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>87</v>
-      </c>
-      <c r="F73" t="s">
-        <v>91</v>
-      </c>
-      <c r="G73" t="s">
-        <v>91</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I73" t="s">
-        <v>167</v>
-      </c>
-      <c r="J73" t="s">
-        <v>168</v>
-      </c>
-      <c r="K73" t="s">
-        <v>169</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" spans="3:13">
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>88</v>
-      </c>
-      <c r="F74" t="s">
-        <v>91</v>
-      </c>
-      <c r="G74" t="s">
-        <v>91</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I74" t="s">
-        <v>167</v>
-      </c>
-      <c r="J74" t="s">
-        <v>168</v>
-      </c>
-      <c r="K74" t="s">
-        <v>169</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="75" spans="3:13">
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F75" t="s">
-        <v>91</v>
-      </c>
-      <c r="G75" t="s">
-        <v>91</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I75" t="s">
-        <v>167</v>
-      </c>
-      <c r="J75" t="s">
-        <v>168</v>
-      </c>
-      <c r="K75" t="s">
-        <v>169</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="3:13">
-      <c r="C76" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" t="s">
-        <v>91</v>
-      </c>
-      <c r="G76" t="s">
-        <v>91</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I76" t="s">
-        <v>167</v>
-      </c>
-      <c r="J76" t="s">
-        <v>168</v>
-      </c>
-      <c r="K76" t="s">
-        <v>169</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3371,125 +2801,95 @@
     <hyperlink ref="H16" r:id="rId29"/>
     <hyperlink ref="M16" r:id="rId30" location="region=0500000US39159"/>
     <hyperlink ref="H17" r:id="rId31"/>
-    <hyperlink ref="M17" r:id="rId32" location="region=0700000US390450695099999"/>
+    <hyperlink ref="M17" r:id="rId32" location="region=1600000US3902680"/>
     <hyperlink ref="H18" r:id="rId33"/>
-    <hyperlink ref="M18" r:id="rId34" location="region=0700000US390458020699999"/>
+    <hyperlink ref="M18" r:id="rId34" location="region=1600000US3905130"/>
     <hyperlink ref="H19" r:id="rId35"/>
-    <hyperlink ref="M19" r:id="rId36" location="region=0700000US390490692299999"/>
+    <hyperlink ref="M19" r:id="rId36" location="region=1600000US3906278"/>
     <hyperlink ref="H20" r:id="rId37"/>
-    <hyperlink ref="M20" r:id="rId38" location="region=0700000US390490944299999"/>
+    <hyperlink ref="M20" r:id="rId38" location="region=1600000US3909890"/>
     <hyperlink ref="H21" r:id="rId39"/>
-    <hyperlink ref="M21" r:id="rId40" location="region=0700000US390491611299999"/>
+    <hyperlink ref="M21" r:id="rId40" location="region=1600000US3911332"/>
     <hyperlink ref="H22" r:id="rId41"/>
-    <hyperlink ref="M22" r:id="rId42" location="region=0700000US390492828099999"/>
+    <hyperlink ref="M22" r:id="rId42" location="region=1600000US3914184"/>
     <hyperlink ref="H23" r:id="rId43"/>
-    <hyperlink ref="M23" r:id="rId44" location="region=0700000US390493777299999"/>
+    <hyperlink ref="M23" r:id="rId44" location="region=1600000US3915070"/>
     <hyperlink ref="H24" r:id="rId45"/>
-    <hyperlink ref="M24" r:id="rId46" location="region=0700000US390493861299999"/>
+    <hyperlink ref="M24" r:id="rId46" location="region=1600000US3918000"/>
     <hyperlink ref="H25" r:id="rId47"/>
-    <hyperlink ref="M25" r:id="rId48" location="region=0700000US390494641099999"/>
+    <hyperlink ref="M25" r:id="rId48" location="region=1600000US3921434"/>
     <hyperlink ref="H26" r:id="rId49"/>
-    <hyperlink ref="M26" r:id="rId50" location="region=0700000US390495006499999"/>
+    <hyperlink ref="M26" r:id="rId50" location="region=1600000US3922694"/>
     <hyperlink ref="H27" r:id="rId51"/>
-    <hyperlink ref="M27" r:id="rId52" location="region=0700000US390496184099999"/>
+    <hyperlink ref="M27" r:id="rId52" location="region=1600000US3929106"/>
     <hyperlink ref="H28" r:id="rId53"/>
-    <hyperlink ref="M28" r:id="rId54" location="region=0700000US390496457099999"/>
+    <hyperlink ref="M28" r:id="rId54" location="region=1600000US3929246"/>
     <hyperlink ref="H29" r:id="rId55"/>
-    <hyperlink ref="M29" r:id="rId56" location="region=0700000US390892569099999"/>
+    <hyperlink ref="M29" r:id="rId56" location="region=1600000US3931304"/>
     <hyperlink ref="H30" r:id="rId57"/>
-    <hyperlink ref="M30" r:id="rId58" location="region=0700000US390893141699999"/>
+    <hyperlink ref="M30" r:id="rId58" location="region=1600000US3931402"/>
     <hyperlink ref="H31" r:id="rId59"/>
-    <hyperlink ref="M31" r:id="rId60" location="region=0700000US391593904699999"/>
+    <hyperlink ref="M31" r:id="rId60" location="region=1600000US3932592"/>
     <hyperlink ref="H32" r:id="rId61"/>
-    <hyperlink ref="M32" r:id="rId62" location="region=1600000US3902680"/>
+    <hyperlink ref="M32" r:id="rId62" location="region=1600000US3932606"/>
     <hyperlink ref="H33" r:id="rId63"/>
-    <hyperlink ref="M33" r:id="rId64" location="region=1600000US3905130"/>
+    <hyperlink ref="M33" r:id="rId64" location="region=1600000US3934748"/>
     <hyperlink ref="H34" r:id="rId65"/>
-    <hyperlink ref="M34" r:id="rId66" location="region=1600000US3906278"/>
+    <hyperlink ref="M34" r:id="rId66" location="region=1600000US3934790"/>
     <hyperlink ref="H35" r:id="rId67"/>
-    <hyperlink ref="M35" r:id="rId68" location="region=1600000US3909890"/>
+    <hyperlink ref="M35" r:id="rId68" location="region=1600000US3935476"/>
     <hyperlink ref="H36" r:id="rId69"/>
-    <hyperlink ref="M36" r:id="rId70" location="region=1600000US3911332"/>
+    <hyperlink ref="M36" r:id="rId70" location="region=1600000US3939340"/>
     <hyperlink ref="H37" r:id="rId71"/>
-    <hyperlink ref="M37" r:id="rId72" location="region=1600000US3914184"/>
+    <hyperlink ref="M37" r:id="rId72" location="region=1600000US3941720"/>
     <hyperlink ref="H38" r:id="rId73"/>
-    <hyperlink ref="M38" r:id="rId74" location="region=1600000US3915070"/>
+    <hyperlink ref="M38" r:id="rId74" location="region=1600000US3944086"/>
     <hyperlink ref="H39" r:id="rId75"/>
-    <hyperlink ref="M39" r:id="rId76" location="region=1600000US3918000"/>
+    <hyperlink ref="M39" r:id="rId76" location="region=1600000US3944674"/>
     <hyperlink ref="H40" r:id="rId77"/>
-    <hyperlink ref="M40" r:id="rId78" location="region=1600000US3921434"/>
+    <hyperlink ref="M40" r:id="rId78" location="region=1600000US3947754"/>
     <hyperlink ref="H41" r:id="rId79"/>
-    <hyperlink ref="M41" r:id="rId80" location="region=1600000US3922694"/>
+    <hyperlink ref="M41" r:id="rId80" location="region=1600000US3948160"/>
     <hyperlink ref="H42" r:id="rId81"/>
-    <hyperlink ref="M42" r:id="rId82" location="region=1600000US3929106"/>
+    <hyperlink ref="M42" r:id="rId82" location="region=1600000US3950862"/>
     <hyperlink ref="H43" r:id="rId83"/>
-    <hyperlink ref="M43" r:id="rId84" location="region=1600000US3929246"/>
+    <hyperlink ref="M43" r:id="rId84" location="region=1600000US3953046"/>
     <hyperlink ref="H44" r:id="rId85"/>
-    <hyperlink ref="M44" r:id="rId86" location="region=1600000US3931304"/>
+    <hyperlink ref="M44" r:id="rId86" location="region=1600000US3953102"/>
     <hyperlink ref="H45" r:id="rId87"/>
-    <hyperlink ref="M45" r:id="rId88" location="region=1600000US3931402"/>
+    <hyperlink ref="M45" r:id="rId88" location="region=1600000US3953970"/>
     <hyperlink ref="H46" r:id="rId89"/>
-    <hyperlink ref="M46" r:id="rId90" location="region=1600000US3932592"/>
+    <hyperlink ref="M46" r:id="rId90" location="region=1600000US3954040"/>
     <hyperlink ref="H47" r:id="rId91"/>
-    <hyperlink ref="M47" r:id="rId92" location="region=1600000US3932606"/>
+    <hyperlink ref="M47" r:id="rId92" location="region=1600000US3954866"/>
     <hyperlink ref="H48" r:id="rId93"/>
-    <hyperlink ref="M48" r:id="rId94" location="region=1600000US3934748"/>
+    <hyperlink ref="M48" r:id="rId94" location="region=1600000US3957862"/>
     <hyperlink ref="H49" r:id="rId95"/>
-    <hyperlink ref="M49" r:id="rId96" location="region=1600000US3934790"/>
+    <hyperlink ref="M49" r:id="rId96" location="region=1600000US3961112"/>
     <hyperlink ref="H50" r:id="rId97"/>
-    <hyperlink ref="M50" r:id="rId98" location="region=1600000US3935476"/>
+    <hyperlink ref="M50" r:id="rId98" location="region=1600000US3962498"/>
     <hyperlink ref="H51" r:id="rId99"/>
-    <hyperlink ref="M51" r:id="rId100" location="region=1600000US3939340"/>
+    <hyperlink ref="M51" r:id="rId100" location="region=1600000US3963030"/>
     <hyperlink ref="H52" r:id="rId101"/>
-    <hyperlink ref="M52" r:id="rId102" location="region=1600000US3941720"/>
+    <hyperlink ref="M52" r:id="rId102" location="region=1600000US3964486"/>
     <hyperlink ref="H53" r:id="rId103"/>
-    <hyperlink ref="M53" r:id="rId104" location="region=1600000US3944086"/>
+    <hyperlink ref="M53" r:id="rId104" location="region=1600000US3966390"/>
     <hyperlink ref="H54" r:id="rId105"/>
-    <hyperlink ref="M54" r:id="rId106" location="region=1600000US3944674"/>
+    <hyperlink ref="M54" r:id="rId106" location="region=1600000US3973068"/>
     <hyperlink ref="H55" r:id="rId107"/>
-    <hyperlink ref="M55" r:id="rId108" location="region=1600000US3947754"/>
+    <hyperlink ref="M55" r:id="rId108" location="region=1600000US3975602"/>
     <hyperlink ref="H56" r:id="rId109"/>
-    <hyperlink ref="M56" r:id="rId110" location="region=1600000US3948160"/>
+    <hyperlink ref="M56" r:id="rId110" location="region=1600000US3979002"/>
     <hyperlink ref="H57" r:id="rId111"/>
-    <hyperlink ref="M57" r:id="rId112" location="region=1600000US3950862"/>
+    <hyperlink ref="M57" r:id="rId112" location="region=1600000US3983342"/>
     <hyperlink ref="H58" r:id="rId113"/>
-    <hyperlink ref="M58" r:id="rId114" location="region=1600000US3953046"/>
+    <hyperlink ref="M58" r:id="rId114" location="region=1600000US3983580"/>
     <hyperlink ref="H59" r:id="rId115"/>
-    <hyperlink ref="M59" r:id="rId116" location="region=1600000US3953102"/>
+    <hyperlink ref="M59" r:id="rId116" location="region=1600000US3984742"/>
     <hyperlink ref="H60" r:id="rId117"/>
-    <hyperlink ref="M60" r:id="rId118" location="region=1600000US3953970"/>
+    <hyperlink ref="M60" r:id="rId118" location="region=1600000US3986604"/>
     <hyperlink ref="H61" r:id="rId119"/>
-    <hyperlink ref="M61" r:id="rId120" location="region=1600000US3954040"/>
-    <hyperlink ref="H62" r:id="rId121"/>
-    <hyperlink ref="M62" r:id="rId122" location="region=1600000US3954866"/>
-    <hyperlink ref="H63" r:id="rId123"/>
-    <hyperlink ref="M63" r:id="rId124" location="region=1600000US3957862"/>
-    <hyperlink ref="H64" r:id="rId125"/>
-    <hyperlink ref="M64" r:id="rId126" location="region=1600000US3961112"/>
-    <hyperlink ref="H65" r:id="rId127"/>
-    <hyperlink ref="M65" r:id="rId128" location="region=1600000US3962498"/>
-    <hyperlink ref="H66" r:id="rId129"/>
-    <hyperlink ref="M66" r:id="rId130" location="region=1600000US3963030"/>
-    <hyperlink ref="H67" r:id="rId131"/>
-    <hyperlink ref="M67" r:id="rId132" location="region=1600000US3964486"/>
-    <hyperlink ref="H68" r:id="rId133"/>
-    <hyperlink ref="M68" r:id="rId134" location="region=1600000US3966390"/>
-    <hyperlink ref="H69" r:id="rId135"/>
-    <hyperlink ref="M69" r:id="rId136" location="region=1600000US3973068"/>
-    <hyperlink ref="H70" r:id="rId137"/>
-    <hyperlink ref="M70" r:id="rId138" location="region=1600000US3975602"/>
-    <hyperlink ref="H71" r:id="rId139"/>
-    <hyperlink ref="M71" r:id="rId140" location="region=1600000US3979002"/>
-    <hyperlink ref="H72" r:id="rId141"/>
-    <hyperlink ref="M72" r:id="rId142" location="region=1600000US3983342"/>
-    <hyperlink ref="H73" r:id="rId143"/>
-    <hyperlink ref="M73" r:id="rId144" location="region=1600000US3983580"/>
-    <hyperlink ref="H74" r:id="rId145"/>
-    <hyperlink ref="M74" r:id="rId146" location="region=1600000US3984742"/>
-    <hyperlink ref="H75" r:id="rId147"/>
-    <hyperlink ref="M75" r:id="rId148" location="region=1600000US3986604"/>
-    <hyperlink ref="H76" r:id="rId149"/>
-    <hyperlink ref="M76" r:id="rId150" location="region=M010000US001"/>
+    <hyperlink ref="M61" r:id="rId120" location="region=M010000US001"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="607">
   <si>
     <t>TileID</t>
   </si>
@@ -109,6 +109,546 @@
     <t>15-County Region</t>
   </si>
   <si>
+    <t>Ashville</t>
+  </si>
+  <si>
+    <t>Baltimore</t>
+  </si>
+  <si>
+    <t>Berkshire Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Berlin Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Concord Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Delaware Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Genoa Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Harlem Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Kingston Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Orange Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Porter Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Scioto Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Trenton Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Troy Township (Delaware)</t>
+  </si>
+  <si>
+    <t>Amanda Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Berne Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Bloom Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Clearcreek Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Greenfield Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Hocking Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Pleasant Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Richland Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Rush Creek Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Violet Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Walnut Township (Fairfield)</t>
+  </si>
+  <si>
+    <t>Union Township (Fayette)</t>
+  </si>
+  <si>
+    <t>Blendon Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Brown Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Clinton Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Franklin Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Hamilton Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Jackson Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Jefferson Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Madison Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Mifflin Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Norwich Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Perry Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Plain Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Pleasant Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Prairie Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Sharon Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Truro Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Washington Township (Franklin)</t>
+  </si>
+  <si>
+    <t>Bellefontaine</t>
+  </si>
+  <si>
+    <t>Bexley</t>
+  </si>
+  <si>
+    <t>Falls Township (Hocking)</t>
+  </si>
+  <si>
+    <t>Green Township (Hocking)</t>
+  </si>
+  <si>
+    <t>Marion Township (Hocking)</t>
+  </si>
+  <si>
+    <t>Brown Township (Knox)</t>
+  </si>
+  <si>
+    <t>Clinton Township (Knox)</t>
+  </si>
+  <si>
+    <t>College Township (Knox)</t>
+  </si>
+  <si>
+    <t>Hilliar Township (Knox)</t>
+  </si>
+  <si>
+    <t>Howard Township (Knox)</t>
+  </si>
+  <si>
+    <t>Monroe Township (Knox)</t>
+  </si>
+  <si>
+    <t>Morris Township (Knox)</t>
+  </si>
+  <si>
+    <t>Union Township (Knox)</t>
+  </si>
+  <si>
+    <t>Etna Township (Licking)</t>
+  </si>
+  <si>
+    <t>Franklin Township (Licking)</t>
+  </si>
+  <si>
+    <t>Granville Township (Licking)</t>
+  </si>
+  <si>
+    <t>Hanover Township (Licking)</t>
+  </si>
+  <si>
+    <t>Harrison Township (Licking)</t>
+  </si>
+  <si>
+    <t>Jersey Township (Licking)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Licking)</t>
+  </si>
+  <si>
+    <t>Licking Township (Licking)</t>
+  </si>
+  <si>
+    <t>Madison Township (Licking)</t>
+  </si>
+  <si>
+    <t>Mary Ann Township (Licking)</t>
+  </si>
+  <si>
+    <t>Monroe Township (Licking)</t>
+  </si>
+  <si>
+    <t>Newark Township (Licking)</t>
+  </si>
+  <si>
+    <t>Newton Township (Licking)</t>
+  </si>
+  <si>
+    <t>St. Albans Township (Licking)</t>
+  </si>
+  <si>
+    <t>Union Township (Licking)</t>
+  </si>
+  <si>
+    <t>Washington Township (Licking)</t>
+  </si>
+  <si>
+    <t>Harrison Township (Logan)</t>
+  </si>
+  <si>
+    <t>Jefferson Township (Logan)</t>
+  </si>
+  <si>
+    <t>Lake Township (Logan)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Logan)</t>
+  </si>
+  <si>
+    <t>McArthur Township (Logan)</t>
+  </si>
+  <si>
+    <t>Miami Township (Logan)</t>
+  </si>
+  <si>
+    <t>Richland Township (Logan)</t>
+  </si>
+  <si>
+    <t>Rushcreek Township (Logan)</t>
+  </si>
+  <si>
+    <t>Stokes Township (Logan)</t>
+  </si>
+  <si>
+    <t>Washington Township (Logan)</t>
+  </si>
+  <si>
+    <t>Canaan Township (Madison)</t>
+  </si>
+  <si>
+    <t>Darby Township (Madison)</t>
+  </si>
+  <si>
+    <t>Jefferson Township (Madison)</t>
+  </si>
+  <si>
+    <t>Pleasant Township (Madison)</t>
+  </si>
+  <si>
+    <t>Somerford Township (Madison)</t>
+  </si>
+  <si>
+    <t>Union Township (Madison)</t>
+  </si>
+  <si>
+    <t>Buckeye Lake</t>
+  </si>
+  <si>
+    <t>Claridon Township (Marion)</t>
+  </si>
+  <si>
+    <t>Marion Township (Marion)</t>
+  </si>
+  <si>
+    <t>Montgomery Township (Marion)</t>
+  </si>
+  <si>
+    <t>Pleasant Township (Marion)</t>
+  </si>
+  <si>
+    <t>Prospect Township (Marion)</t>
+  </si>
+  <si>
+    <t>Canal Winchester</t>
+  </si>
+  <si>
+    <t>Bennington Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Cardington Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Chester Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Congress Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Gilead Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Harmony Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Lincoln Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Perry Township (Morrow)</t>
+  </si>
+  <si>
+    <t>Cardington</t>
+  </si>
+  <si>
+    <t>Harrison Township (Perry)</t>
+  </si>
+  <si>
+    <t>Jackson Township (Perry)</t>
+  </si>
+  <si>
+    <t>Pike Township (Perry)</t>
+  </si>
+  <si>
+    <t>Reading Township (Perry)</t>
+  </si>
+  <si>
+    <t>Circleville Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Darby Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Harrison Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Pickaway Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Saltcreek Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Scioto Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Walnut Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Washington Township (Pickaway)</t>
+  </si>
+  <si>
+    <t>Buckskin Township (Ross)</t>
+  </si>
+  <si>
+    <t>Concord Township (Ross)</t>
+  </si>
+  <si>
+    <t>Huntington Township (Ross)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Ross)</t>
+  </si>
+  <si>
+    <t>Paxton Township (Ross)</t>
+  </si>
+  <si>
+    <t>Scioto Township (Ross)</t>
+  </si>
+  <si>
+    <t>Springfield Township (Ross)</t>
+  </si>
+  <si>
+    <t>Twin Township (Ross)</t>
+  </si>
+  <si>
+    <t>Chillicothe</t>
+  </si>
+  <si>
+    <t>Circleville</t>
+  </si>
+  <si>
+    <t>Allen Township (Union)</t>
+  </si>
+  <si>
+    <t>Claibourne Township (Union)</t>
+  </si>
+  <si>
+    <t>Darby Township (Union)</t>
+  </si>
+  <si>
+    <t>Dover Township (Union)</t>
+  </si>
+  <si>
+    <t>Jerome Township (Union)</t>
+  </si>
+  <si>
+    <t>Liberty Township (Union)</t>
+  </si>
+  <si>
+    <t>Paris Township (Union)</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>Commercial Point</t>
+  </si>
+  <si>
+    <t>Crooksville</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>Fredericktown</t>
+  </si>
+  <si>
+    <t>Gahanna</t>
+  </si>
+  <si>
+    <t>Gambier</t>
+  </si>
+  <si>
+    <t>Grandview Heights</t>
+  </si>
+  <si>
+    <t>Granville</t>
+  </si>
+  <si>
+    <t>Grove City</t>
+  </si>
+  <si>
+    <t>Groveport</t>
+  </si>
+  <si>
+    <t>Heath</t>
+  </si>
+  <si>
+    <t>Hebron</t>
+  </si>
+  <si>
+    <t>Hilliard</t>
+  </si>
+  <si>
+    <t>Johnstown</t>
+  </si>
+  <si>
+    <t>Lancaster</t>
+  </si>
+  <si>
+    <t>Lithopolis</t>
+  </si>
+  <si>
+    <t>Logan</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Marion</t>
+  </si>
+  <si>
+    <t>Marysville</t>
+  </si>
+  <si>
+    <t>Minerva Park</t>
+  </si>
+  <si>
+    <t>Mount Gilead</t>
+  </si>
+  <si>
+    <t>Mount Sterling</t>
+  </si>
+  <si>
+    <t>Mount Vernon</t>
+  </si>
+  <si>
+    <t>New Albany</t>
+  </si>
+  <si>
+    <t>Newark</t>
+  </si>
+  <si>
+    <t>New Lexington</t>
+  </si>
+  <si>
+    <t>Obetz</t>
+  </si>
+  <si>
+    <t>Pataskala</t>
+  </si>
+  <si>
+    <t>Pickerington</t>
+  </si>
+  <si>
+    <t>Plain City</t>
+  </si>
+  <si>
+    <t>Powell</t>
+  </si>
+  <si>
+    <t>Reynoldsburg</t>
+  </si>
+  <si>
+    <t>Richwood</t>
+  </si>
+  <si>
+    <t>South Bloomfield</t>
+  </si>
+  <si>
+    <t>Sunbury</t>
+  </si>
+  <si>
+    <t>Upper Arlington</t>
+  </si>
+  <si>
+    <t>Utica</t>
+  </si>
+  <si>
+    <t>Washington Court House</t>
+  </si>
+  <si>
+    <t>Westerville</t>
+  </si>
+  <si>
+    <t>West Jefferson</t>
+  </si>
+  <si>
+    <t>Whitehall</t>
+  </si>
+  <si>
+    <t>Worthington</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
@@ -160,10 +700,550 @@
     <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M010000US001.svg</t>
   </si>
   <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3902680.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3903758.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390410577499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390410578899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390411814099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390412144899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390412969499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390413351699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390414036299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390414310699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390415861899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390416417899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390417084299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390417733699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390417756099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390450163799999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390450595699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390450695099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390451568699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390453206099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390453581299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390454312099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390456324099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390456668499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390456912099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390458020699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390458057099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390477831699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390490692299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390490944299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390491611299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390492828099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390493302699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390493777299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390493861299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390494641099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390495006499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390495734499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390496184099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390496297499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390496325499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390496457099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390497178799999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390497771499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390498124299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3905130.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3906278.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390732648899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390733178099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390734774099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390830947099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390831614099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390831668699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390833546299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390833652699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390835143699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390835229099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390837835899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390892569099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390892833699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390893141699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390893329999999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390893389499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390893910299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390894323299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390894345699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390894650899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390894813299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390895145099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390895405499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390895558099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390896945699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390897840099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390898141099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390913390899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390913868299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390914128699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390914324699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390914568299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390914937899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390916674099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390916913499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390917478099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390918142499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390971123499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390972014299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390973869699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390976333899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390977296099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US390977842899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3909890.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391011519699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391014776899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391015173099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391016335299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391016479499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3911332.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391170550899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391171209899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391171403099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391171829499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391173012899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391173360099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391174368099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391176198099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3912084.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391273396499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391273796899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391276268099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391276576099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391291507799999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391292015699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391293397899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391296248499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391297018499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391297087099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391298059899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391298155099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391411001699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391411823899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391413689099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391414330299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391416130899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391417089899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391417412999999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391417800899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3914184.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3915070.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391590133699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391591511299999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391592017099999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391592248499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391593904699999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391594335899999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US391595986499999.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3918000.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3918070.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3919456.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3921434.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3922694.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3928658.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3929106.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3929246.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3931304.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3931402.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3932592.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3932606.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3934748.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3934790.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3935476.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3939340.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3941720.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3944086.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3944632.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3944674.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3947754.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3948160.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3950862.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3952738.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3953046.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3953102.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3953970.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3954040.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3954866.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3957862.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3961112.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3962498.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3963030.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3964486.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3966390.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3966936.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3973068.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3975602.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3979002.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3979114.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3981718.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3983342.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3983580.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3984742.svg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/pop-temporal/refs/heads/main/output_data/charts/M100000US3986604.svg</t>
+  </si>
+  <si>
     <t>Mid-Ohio Regional Planning Commission</t>
   </si>
   <si>
-    <t>2025</t>
+    <t>2026</t>
   </si>
   <si>
     <t>annually</t>
@@ -215,6 +1295,546 @@
   </si>
   <si>
     <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M010000US001</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3902680</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3903758</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390410577499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390410578899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390411814099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390412144899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390412969499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390413351699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390414036299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390414310699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390415861899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390416417899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390417084299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390417733699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390417756099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390450163799999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390450595699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390450695099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390451568699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390453206099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390453581299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390454312099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390456324099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390456668499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390456912099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390458020699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390458057099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390477831699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390490692299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390490944299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390491611299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390492828099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390493302699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390493777299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390493861299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390494641099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390495006499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390495734499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390496184099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390496297499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390496325499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390496457099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390497178799999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390497771499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390498124299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3905130</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3906278</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390732648899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390733178099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390734774099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390830947099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390831614099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390831668699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390833546299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390833652699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390835143699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390835229099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390837835899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390892569099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390892833699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390893141699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390893329999999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390893389499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390893910299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390894323299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390894345699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390894650899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390894813299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390895145099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390895405499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390895558099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390896945699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390897840099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390898141099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390913390899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390913868299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390914128699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390914324699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390914568299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390914937899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390916674099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390916913499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390917478099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390918142499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390971123499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390972014299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390973869699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390976333899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390977296099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US390977842899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3909890</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391011519699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391014776899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391015173099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391016335299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391016479499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3911332</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391170550899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391171209899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391171403099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391171829499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391173012899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391173360099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391174368099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391176198099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3912084</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391273396499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391273796899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391276268099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391276576099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391291507799999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391292015699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391293397899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391296248499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391297018499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391297087099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391298059899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391298155099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391411001699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391411823899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391413689099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391414330299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391416130899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391417089899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391417412999999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391417800899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3914184</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3915070</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391590133699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391591511299999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391592017099999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391592248499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391593904699999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391594335899999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US391595986499999</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3918000</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3918070</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3919456</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3921434</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3922694</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3928658</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3929106</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3929246</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3931304</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3931402</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3932592</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3932606</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3934748</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3934790</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3935476</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3939340</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3941720</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3944086</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3944632</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3944674</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3947754</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3948160</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3950862</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3952738</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3953046</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3953102</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3953970</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3954040</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3954866</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3957862</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3961112</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3962498</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3963030</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3964486</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3966390</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3966936</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3973068</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3975602</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3979002</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3979114</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3981718</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3983342</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3983580</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3984742</t>
+  </si>
+  <si>
+    <t>https://morpc.maps.arcgis.com/apps/dashboards/d1291225631545438293bdfcfffaef6b#region=M100000US3986604</t>
   </si>
 </sst>
 </file>
@@ -585,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -637,25 +2257,25 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>51</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -666,25 +2286,25 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>52</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -695,25 +2315,25 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>214</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>53</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -724,25 +2344,25 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -753,25 +2373,25 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K6" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>55</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -782,25 +2402,25 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>56</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -811,25 +2431,25 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>57</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -840,25 +2460,25 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>58</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -869,25 +2489,25 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K10" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>59</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -898,25 +2518,25 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>41</v>
+        <v>221</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>60</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -927,25 +2547,25 @@
         <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>61</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -956,25 +2576,25 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K13" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>62</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -985,25 +2605,25 @@
         <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>44</v>
+        <v>224</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K14" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>63</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1014,25 +2634,25 @@
         <v>28</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K15" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>64</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1043,25 +2663,25 @@
         <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="K16" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>65</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="3:13">
@@ -1072,25 +2692,4705 @@
         <v>30</v>
       </c>
       <c r="F17" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I17" t="s">
+        <v>408</v>
+      </c>
+      <c r="J17" t="s">
+        <v>409</v>
+      </c>
+      <c r="K17" t="s">
+        <v>410</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13">
+      <c r="D18" t="s">
         <v>31</v>
       </c>
-      <c r="G17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="F18" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" t="s">
+        <v>211</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I18" t="s">
+        <v>408</v>
+      </c>
+      <c r="J18" t="s">
+        <v>409</v>
+      </c>
+      <c r="K18" t="s">
+        <v>410</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13">
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I19" t="s">
+        <v>408</v>
+      </c>
+      <c r="J19" t="s">
+        <v>409</v>
+      </c>
+      <c r="K19" t="s">
+        <v>410</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13">
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I20" t="s">
+        <v>408</v>
+      </c>
+      <c r="J20" t="s">
+        <v>409</v>
+      </c>
+      <c r="K20" t="s">
+        <v>410</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13">
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>211</v>
+      </c>
+      <c r="G21" t="s">
+        <v>211</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I21" t="s">
+        <v>408</v>
+      </c>
+      <c r="J21" t="s">
+        <v>409</v>
+      </c>
+      <c r="K21" t="s">
+        <v>410</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13">
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>211</v>
+      </c>
+      <c r="G22" t="s">
+        <v>211</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I22" t="s">
+        <v>408</v>
+      </c>
+      <c r="J22" t="s">
+        <v>409</v>
+      </c>
+      <c r="K22" t="s">
+        <v>410</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13">
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>211</v>
+      </c>
+      <c r="G23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I23" t="s">
+        <v>408</v>
+      </c>
+      <c r="J23" t="s">
+        <v>409</v>
+      </c>
+      <c r="K23" t="s">
+        <v>410</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13">
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>211</v>
+      </c>
+      <c r="G24" t="s">
+        <v>211</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I24" t="s">
+        <v>408</v>
+      </c>
+      <c r="J24" t="s">
+        <v>409</v>
+      </c>
+      <c r="K24" t="s">
+        <v>410</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13">
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" t="s">
+        <v>211</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I25" t="s">
+        <v>408</v>
+      </c>
+      <c r="J25" t="s">
+        <v>409</v>
+      </c>
+      <c r="K25" t="s">
+        <v>410</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13">
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>211</v>
+      </c>
+      <c r="G26" t="s">
+        <v>211</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I26" t="s">
+        <v>408</v>
+      </c>
+      <c r="J26" t="s">
+        <v>409</v>
+      </c>
+      <c r="K26" t="s">
+        <v>410</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13">
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>211</v>
+      </c>
+      <c r="G27" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I27" t="s">
+        <v>408</v>
+      </c>
+      <c r="J27" t="s">
+        <v>409</v>
+      </c>
+      <c r="K27" t="s">
+        <v>410</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13">
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>211</v>
+      </c>
+      <c r="G28" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I28" t="s">
+        <v>408</v>
+      </c>
+      <c r="J28" t="s">
+        <v>409</v>
+      </c>
+      <c r="K28" t="s">
+        <v>410</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13">
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>211</v>
+      </c>
+      <c r="G29" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I29" t="s">
+        <v>408</v>
+      </c>
+      <c r="J29" t="s">
+        <v>409</v>
+      </c>
+      <c r="K29" t="s">
+        <v>410</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13">
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" t="s">
+        <v>211</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I30" t="s">
+        <v>408</v>
+      </c>
+      <c r="J30" t="s">
+        <v>409</v>
+      </c>
+      <c r="K30" t="s">
+        <v>410</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13">
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
+        <v>211</v>
+      </c>
+      <c r="G31" t="s">
+        <v>211</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I31" t="s">
+        <v>408</v>
+      </c>
+      <c r="J31" t="s">
+        <v>409</v>
+      </c>
+      <c r="K31" t="s">
+        <v>410</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13">
+      <c r="D32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" t="s">
+        <v>211</v>
+      </c>
+      <c r="G32" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" t="s">
+        <v>408</v>
+      </c>
+      <c r="J32" t="s">
+        <v>409</v>
+      </c>
+      <c r="K32" t="s">
+        <v>410</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13">
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I33" t="s">
+        <v>408</v>
+      </c>
+      <c r="J33" t="s">
+        <v>409</v>
+      </c>
+      <c r="K33" t="s">
+        <v>410</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13">
+      <c r="D34" t="s">
         <v>47</v>
       </c>
-      <c r="I17" t="s">
+      <c r="F34" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I34" t="s">
+        <v>408</v>
+      </c>
+      <c r="J34" t="s">
+        <v>409</v>
+      </c>
+      <c r="K34" t="s">
+        <v>410</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13">
+      <c r="D35" t="s">
         <v>48</v>
       </c>
-      <c r="J17" t="s">
+      <c r="F35" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" t="s">
+        <v>211</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I35" t="s">
+        <v>408</v>
+      </c>
+      <c r="J35" t="s">
+        <v>409</v>
+      </c>
+      <c r="K35" t="s">
+        <v>410</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13">
+      <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="K17" t="s">
+      <c r="F36" t="s">
+        <v>211</v>
+      </c>
+      <c r="G36" t="s">
+        <v>211</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I36" t="s">
+        <v>408</v>
+      </c>
+      <c r="J36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K36" t="s">
+        <v>410</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13">
+      <c r="D37" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="F37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G37" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J37" t="s">
+        <v>409</v>
+      </c>
+      <c r="K37" t="s">
+        <v>410</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13">
+      <c r="D38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" t="s">
+        <v>211</v>
+      </c>
+      <c r="G38" t="s">
+        <v>211</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J38" t="s">
+        <v>409</v>
+      </c>
+      <c r="K38" t="s">
+        <v>410</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13">
+      <c r="D39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" t="s">
+        <v>211</v>
+      </c>
+      <c r="G39" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J39" t="s">
+        <v>409</v>
+      </c>
+      <c r="K39" t="s">
+        <v>410</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13">
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" t="s">
+        <v>211</v>
+      </c>
+      <c r="G40" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I40" t="s">
+        <v>408</v>
+      </c>
+      <c r="J40" t="s">
+        <v>409</v>
+      </c>
+      <c r="K40" t="s">
+        <v>410</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13">
+      <c r="D41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
+        <v>211</v>
+      </c>
+      <c r="G41" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I41" t="s">
+        <v>408</v>
+      </c>
+      <c r="J41" t="s">
+        <v>409</v>
+      </c>
+      <c r="K41" t="s">
+        <v>410</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13">
+      <c r="D42" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" t="s">
+        <v>211</v>
+      </c>
+      <c r="G42" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I42" t="s">
+        <v>408</v>
+      </c>
+      <c r="J42" t="s">
+        <v>409</v>
+      </c>
+      <c r="K42" t="s">
+        <v>410</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13">
+      <c r="D43" t="s">
+        <v>56</v>
+      </c>
+      <c r="F43" t="s">
+        <v>211</v>
+      </c>
+      <c r="G43" t="s">
+        <v>211</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I43" t="s">
+        <v>408</v>
+      </c>
+      <c r="J43" t="s">
+        <v>409</v>
+      </c>
+      <c r="K43" t="s">
+        <v>410</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13">
+      <c r="D44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" t="s">
+        <v>211</v>
+      </c>
+      <c r="G44" t="s">
+        <v>211</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" t="s">
+        <v>408</v>
+      </c>
+      <c r="J44" t="s">
+        <v>409</v>
+      </c>
+      <c r="K44" t="s">
+        <v>410</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="4:13">
+      <c r="D45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" t="s">
+        <v>211</v>
+      </c>
+      <c r="G45" t="s">
+        <v>211</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I45" t="s">
+        <v>408</v>
+      </c>
+      <c r="J45" t="s">
+        <v>409</v>
+      </c>
+      <c r="K45" t="s">
+        <v>410</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="4:13">
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" t="s">
+        <v>211</v>
+      </c>
+      <c r="G46" t="s">
+        <v>211</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I46" t="s">
+        <v>408</v>
+      </c>
+      <c r="J46" t="s">
+        <v>409</v>
+      </c>
+      <c r="K46" t="s">
+        <v>410</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="4:13">
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+      <c r="F47" t="s">
+        <v>211</v>
+      </c>
+      <c r="G47" t="s">
+        <v>211</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I47" t="s">
+        <v>408</v>
+      </c>
+      <c r="J47" t="s">
+        <v>409</v>
+      </c>
+      <c r="K47" t="s">
+        <v>410</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13">
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" t="s">
+        <v>211</v>
+      </c>
+      <c r="G48" t="s">
+        <v>211</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I48" t="s">
+        <v>408</v>
+      </c>
+      <c r="J48" t="s">
+        <v>409</v>
+      </c>
+      <c r="K48" t="s">
+        <v>410</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="4:13">
+      <c r="D49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" t="s">
+        <v>211</v>
+      </c>
+      <c r="G49" t="s">
+        <v>211</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I49" t="s">
+        <v>408</v>
+      </c>
+      <c r="J49" t="s">
+        <v>409</v>
+      </c>
+      <c r="K49" t="s">
+        <v>410</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="4:13">
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" t="s">
+        <v>211</v>
+      </c>
+      <c r="G50" t="s">
+        <v>211</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I50" t="s">
+        <v>408</v>
+      </c>
+      <c r="J50" t="s">
+        <v>409</v>
+      </c>
+      <c r="K50" t="s">
+        <v>410</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="4:13">
+      <c r="D51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" t="s">
+        <v>211</v>
+      </c>
+      <c r="G51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I51" t="s">
+        <v>408</v>
+      </c>
+      <c r="J51" t="s">
+        <v>409</v>
+      </c>
+      <c r="K51" t="s">
+        <v>410</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="4:13">
+      <c r="D52" t="s">
+        <v>65</v>
+      </c>
+      <c r="F52" t="s">
+        <v>211</v>
+      </c>
+      <c r="G52" t="s">
+        <v>211</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I52" t="s">
+        <v>408</v>
+      </c>
+      <c r="J52" t="s">
+        <v>409</v>
+      </c>
+      <c r="K52" t="s">
+        <v>410</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13">
+      <c r="D53" t="s">
         <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>211</v>
+      </c>
+      <c r="G53" t="s">
+        <v>211</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I53" t="s">
+        <v>408</v>
+      </c>
+      <c r="J53" t="s">
+        <v>409</v>
+      </c>
+      <c r="K53" t="s">
+        <v>410</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="4:13">
+      <c r="D54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F54" t="s">
+        <v>211</v>
+      </c>
+      <c r="G54" t="s">
+        <v>211</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I54" t="s">
+        <v>408</v>
+      </c>
+      <c r="J54" t="s">
+        <v>409</v>
+      </c>
+      <c r="K54" t="s">
+        <v>410</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13">
+      <c r="D55" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" t="s">
+        <v>211</v>
+      </c>
+      <c r="G55" t="s">
+        <v>211</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I55" t="s">
+        <v>408</v>
+      </c>
+      <c r="J55" t="s">
+        <v>409</v>
+      </c>
+      <c r="K55" t="s">
+        <v>410</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56" spans="4:13">
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" t="s">
+        <v>211</v>
+      </c>
+      <c r="G56" t="s">
+        <v>211</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I56" t="s">
+        <v>408</v>
+      </c>
+      <c r="J56" t="s">
+        <v>409</v>
+      </c>
+      <c r="K56" t="s">
+        <v>410</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="4:13">
+      <c r="D57" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" t="s">
+        <v>211</v>
+      </c>
+      <c r="G57" t="s">
+        <v>211</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I57" t="s">
+        <v>408</v>
+      </c>
+      <c r="J57" t="s">
+        <v>409</v>
+      </c>
+      <c r="K57" t="s">
+        <v>410</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="4:13">
+      <c r="D58" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" t="s">
+        <v>211</v>
+      </c>
+      <c r="G58" t="s">
+        <v>211</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I58" t="s">
+        <v>408</v>
+      </c>
+      <c r="J58" t="s">
+        <v>409</v>
+      </c>
+      <c r="K58" t="s">
+        <v>410</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="4:13">
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" t="s">
+        <v>211</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I59" t="s">
+        <v>408</v>
+      </c>
+      <c r="J59" t="s">
+        <v>409</v>
+      </c>
+      <c r="K59" t="s">
+        <v>410</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="4:13">
+      <c r="D60" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" t="s">
+        <v>211</v>
+      </c>
+      <c r="G60" t="s">
+        <v>211</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I60" t="s">
+        <v>408</v>
+      </c>
+      <c r="J60" t="s">
+        <v>409</v>
+      </c>
+      <c r="K60" t="s">
+        <v>410</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="4:13">
+      <c r="D61" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>211</v>
+      </c>
+      <c r="G61" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I61" t="s">
+        <v>408</v>
+      </c>
+      <c r="J61" t="s">
+        <v>409</v>
+      </c>
+      <c r="K61" t="s">
+        <v>410</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="62" spans="4:13">
+      <c r="D62" t="s">
+        <v>75</v>
+      </c>
+      <c r="F62" t="s">
+        <v>211</v>
+      </c>
+      <c r="G62" t="s">
+        <v>211</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I62" t="s">
+        <v>408</v>
+      </c>
+      <c r="J62" t="s">
+        <v>409</v>
+      </c>
+      <c r="K62" t="s">
+        <v>410</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="63" spans="4:13">
+      <c r="D63" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63" t="s">
+        <v>211</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I63" t="s">
+        <v>408</v>
+      </c>
+      <c r="J63" t="s">
+        <v>409</v>
+      </c>
+      <c r="K63" t="s">
+        <v>410</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="64" spans="4:13">
+      <c r="D64" t="s">
+        <v>77</v>
+      </c>
+      <c r="F64" t="s">
+        <v>211</v>
+      </c>
+      <c r="G64" t="s">
+        <v>211</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I64" t="s">
+        <v>408</v>
+      </c>
+      <c r="J64" t="s">
+        <v>409</v>
+      </c>
+      <c r="K64" t="s">
+        <v>410</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="65" spans="4:13">
+      <c r="D65" t="s">
+        <v>78</v>
+      </c>
+      <c r="F65" t="s">
+        <v>211</v>
+      </c>
+      <c r="G65" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I65" t="s">
+        <v>408</v>
+      </c>
+      <c r="J65" t="s">
+        <v>409</v>
+      </c>
+      <c r="K65" t="s">
+        <v>410</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" spans="4:13">
+      <c r="D66" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66" t="s">
+        <v>211</v>
+      </c>
+      <c r="G66" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I66" t="s">
+        <v>408</v>
+      </c>
+      <c r="J66" t="s">
+        <v>409</v>
+      </c>
+      <c r="K66" t="s">
+        <v>410</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="4:13">
+      <c r="D67" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" t="s">
+        <v>211</v>
+      </c>
+      <c r="G67" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I67" t="s">
+        <v>408</v>
+      </c>
+      <c r="J67" t="s">
+        <v>409</v>
+      </c>
+      <c r="K67" t="s">
+        <v>410</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="68" spans="4:13">
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68" t="s">
+        <v>211</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I68" t="s">
+        <v>408</v>
+      </c>
+      <c r="J68" t="s">
+        <v>409</v>
+      </c>
+      <c r="K68" t="s">
+        <v>410</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="69" spans="4:13">
+      <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="F69" t="s">
+        <v>211</v>
+      </c>
+      <c r="G69" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I69" t="s">
+        <v>408</v>
+      </c>
+      <c r="J69" t="s">
+        <v>409</v>
+      </c>
+      <c r="K69" t="s">
+        <v>410</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="70" spans="4:13">
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+      <c r="F70" t="s">
+        <v>211</v>
+      </c>
+      <c r="G70" t="s">
+        <v>211</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I70" t="s">
+        <v>408</v>
+      </c>
+      <c r="J70" t="s">
+        <v>409</v>
+      </c>
+      <c r="K70" t="s">
+        <v>410</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="71" spans="4:13">
+      <c r="D71" t="s">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s">
+        <v>211</v>
+      </c>
+      <c r="G71" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I71" t="s">
+        <v>408</v>
+      </c>
+      <c r="J71" t="s">
+        <v>409</v>
+      </c>
+      <c r="K71" t="s">
+        <v>410</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="4:13">
+      <c r="D72" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" t="s">
+        <v>211</v>
+      </c>
+      <c r="G72" t="s">
+        <v>211</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I72" t="s">
+        <v>408</v>
+      </c>
+      <c r="J72" t="s">
+        <v>409</v>
+      </c>
+      <c r="K72" t="s">
+        <v>410</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="73" spans="4:13">
+      <c r="D73" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" t="s">
+        <v>211</v>
+      </c>
+      <c r="G73" t="s">
+        <v>211</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I73" t="s">
+        <v>408</v>
+      </c>
+      <c r="J73" t="s">
+        <v>409</v>
+      </c>
+      <c r="K73" t="s">
+        <v>410</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="74" spans="4:13">
+      <c r="D74" t="s">
+        <v>87</v>
+      </c>
+      <c r="F74" t="s">
+        <v>211</v>
+      </c>
+      <c r="G74" t="s">
+        <v>211</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I74" t="s">
+        <v>408</v>
+      </c>
+      <c r="J74" t="s">
+        <v>409</v>
+      </c>
+      <c r="K74" t="s">
+        <v>410</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="75" spans="4:13">
+      <c r="D75" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" t="s">
+        <v>211</v>
+      </c>
+      <c r="G75" t="s">
+        <v>211</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I75" t="s">
+        <v>408</v>
+      </c>
+      <c r="J75" t="s">
+        <v>409</v>
+      </c>
+      <c r="K75" t="s">
+        <v>410</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="76" spans="4:13">
+      <c r="D76" t="s">
+        <v>89</v>
+      </c>
+      <c r="F76" t="s">
+        <v>211</v>
+      </c>
+      <c r="G76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I76" t="s">
+        <v>408</v>
+      </c>
+      <c r="J76" t="s">
+        <v>409</v>
+      </c>
+      <c r="K76" t="s">
+        <v>410</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="77" spans="4:13">
+      <c r="D77" t="s">
+        <v>90</v>
+      </c>
+      <c r="F77" t="s">
+        <v>211</v>
+      </c>
+      <c r="G77" t="s">
+        <v>211</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I77" t="s">
+        <v>408</v>
+      </c>
+      <c r="J77" t="s">
+        <v>409</v>
+      </c>
+      <c r="K77" t="s">
+        <v>410</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="78" spans="4:13">
+      <c r="D78" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" t="s">
+        <v>211</v>
+      </c>
+      <c r="G78" t="s">
+        <v>211</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I78" t="s">
+        <v>408</v>
+      </c>
+      <c r="J78" t="s">
+        <v>409</v>
+      </c>
+      <c r="K78" t="s">
+        <v>410</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="79" spans="4:13">
+      <c r="D79" t="s">
+        <v>92</v>
+      </c>
+      <c r="F79" t="s">
+        <v>211</v>
+      </c>
+      <c r="G79" t="s">
+        <v>211</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I79" t="s">
+        <v>408</v>
+      </c>
+      <c r="J79" t="s">
+        <v>409</v>
+      </c>
+      <c r="K79" t="s">
+        <v>410</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="80" spans="4:13">
+      <c r="D80" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" t="s">
+        <v>211</v>
+      </c>
+      <c r="G80" t="s">
+        <v>211</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I80" t="s">
+        <v>408</v>
+      </c>
+      <c r="J80" t="s">
+        <v>409</v>
+      </c>
+      <c r="K80" t="s">
+        <v>410</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="81" spans="4:13">
+      <c r="D81" t="s">
+        <v>94</v>
+      </c>
+      <c r="F81" t="s">
+        <v>211</v>
+      </c>
+      <c r="G81" t="s">
+        <v>211</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I81" t="s">
+        <v>408</v>
+      </c>
+      <c r="J81" t="s">
+        <v>409</v>
+      </c>
+      <c r="K81" t="s">
+        <v>410</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="82" spans="4:13">
+      <c r="D82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>211</v>
+      </c>
+      <c r="G82" t="s">
+        <v>211</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I82" t="s">
+        <v>408</v>
+      </c>
+      <c r="J82" t="s">
+        <v>409</v>
+      </c>
+      <c r="K82" t="s">
+        <v>410</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="83" spans="4:13">
+      <c r="D83" t="s">
+        <v>96</v>
+      </c>
+      <c r="F83" t="s">
+        <v>211</v>
+      </c>
+      <c r="G83" t="s">
+        <v>211</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I83" t="s">
+        <v>408</v>
+      </c>
+      <c r="J83" t="s">
+        <v>409</v>
+      </c>
+      <c r="K83" t="s">
+        <v>410</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="84" spans="4:13">
+      <c r="D84" t="s">
+        <v>97</v>
+      </c>
+      <c r="F84" t="s">
+        <v>211</v>
+      </c>
+      <c r="G84" t="s">
+        <v>211</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I84" t="s">
+        <v>408</v>
+      </c>
+      <c r="J84" t="s">
+        <v>409</v>
+      </c>
+      <c r="K84" t="s">
+        <v>410</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="85" spans="4:13">
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+      <c r="F85" t="s">
+        <v>211</v>
+      </c>
+      <c r="G85" t="s">
+        <v>211</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I85" t="s">
+        <v>408</v>
+      </c>
+      <c r="J85" t="s">
+        <v>409</v>
+      </c>
+      <c r="K85" t="s">
+        <v>410</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="86" spans="4:13">
+      <c r="D86" t="s">
+        <v>99</v>
+      </c>
+      <c r="F86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G86" t="s">
+        <v>211</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I86" t="s">
+        <v>408</v>
+      </c>
+      <c r="J86" t="s">
+        <v>409</v>
+      </c>
+      <c r="K86" t="s">
+        <v>410</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="87" spans="4:13">
+      <c r="D87" t="s">
+        <v>100</v>
+      </c>
+      <c r="F87" t="s">
+        <v>211</v>
+      </c>
+      <c r="G87" t="s">
+        <v>211</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I87" t="s">
+        <v>408</v>
+      </c>
+      <c r="J87" t="s">
+        <v>409</v>
+      </c>
+      <c r="K87" t="s">
+        <v>410</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="88" spans="4:13">
+      <c r="D88" t="s">
+        <v>101</v>
+      </c>
+      <c r="F88" t="s">
+        <v>211</v>
+      </c>
+      <c r="G88" t="s">
+        <v>211</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I88" t="s">
+        <v>408</v>
+      </c>
+      <c r="J88" t="s">
+        <v>409</v>
+      </c>
+      <c r="K88" t="s">
+        <v>410</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="89" spans="4:13">
+      <c r="D89" t="s">
+        <v>102</v>
+      </c>
+      <c r="F89" t="s">
+        <v>211</v>
+      </c>
+      <c r="G89" t="s">
+        <v>211</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I89" t="s">
+        <v>408</v>
+      </c>
+      <c r="J89" t="s">
+        <v>409</v>
+      </c>
+      <c r="K89" t="s">
+        <v>410</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="90" spans="4:13">
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" t="s">
+        <v>211</v>
+      </c>
+      <c r="G90" t="s">
+        <v>211</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I90" t="s">
+        <v>408</v>
+      </c>
+      <c r="J90" t="s">
+        <v>409</v>
+      </c>
+      <c r="K90" t="s">
+        <v>410</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="91" spans="4:13">
+      <c r="D91" t="s">
+        <v>104</v>
+      </c>
+      <c r="F91" t="s">
+        <v>211</v>
+      </c>
+      <c r="G91" t="s">
+        <v>211</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I91" t="s">
+        <v>408</v>
+      </c>
+      <c r="J91" t="s">
+        <v>409</v>
+      </c>
+      <c r="K91" t="s">
+        <v>410</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="92" spans="4:13">
+      <c r="D92" t="s">
+        <v>105</v>
+      </c>
+      <c r="F92" t="s">
+        <v>211</v>
+      </c>
+      <c r="G92" t="s">
+        <v>211</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I92" t="s">
+        <v>408</v>
+      </c>
+      <c r="J92" t="s">
+        <v>409</v>
+      </c>
+      <c r="K92" t="s">
+        <v>410</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="93" spans="4:13">
+      <c r="D93" t="s">
+        <v>106</v>
+      </c>
+      <c r="F93" t="s">
+        <v>211</v>
+      </c>
+      <c r="G93" t="s">
+        <v>211</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="I93" t="s">
+        <v>408</v>
+      </c>
+      <c r="J93" t="s">
+        <v>409</v>
+      </c>
+      <c r="K93" t="s">
+        <v>410</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="94" spans="4:13">
+      <c r="D94" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" t="s">
+        <v>211</v>
+      </c>
+      <c r="G94" t="s">
+        <v>211</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I94" t="s">
+        <v>408</v>
+      </c>
+      <c r="J94" t="s">
+        <v>409</v>
+      </c>
+      <c r="K94" t="s">
+        <v>410</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="95" spans="4:13">
+      <c r="D95" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95" t="s">
+        <v>211</v>
+      </c>
+      <c r="G95" t="s">
+        <v>211</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I95" t="s">
+        <v>408</v>
+      </c>
+      <c r="J95" t="s">
+        <v>409</v>
+      </c>
+      <c r="K95" t="s">
+        <v>410</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="96" spans="4:13">
+      <c r="D96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
+        <v>211</v>
+      </c>
+      <c r="G96" t="s">
+        <v>211</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I96" t="s">
+        <v>408</v>
+      </c>
+      <c r="J96" t="s">
+        <v>409</v>
+      </c>
+      <c r="K96" t="s">
+        <v>410</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="97" spans="4:13">
+      <c r="D97" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97" t="s">
+        <v>211</v>
+      </c>
+      <c r="G97" t="s">
+        <v>211</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I97" t="s">
+        <v>408</v>
+      </c>
+      <c r="J97" t="s">
+        <v>409</v>
+      </c>
+      <c r="K97" t="s">
+        <v>410</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="98" spans="4:13">
+      <c r="D98" t="s">
+        <v>111</v>
+      </c>
+      <c r="F98" t="s">
+        <v>211</v>
+      </c>
+      <c r="G98" t="s">
+        <v>211</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I98" t="s">
+        <v>408</v>
+      </c>
+      <c r="J98" t="s">
+        <v>409</v>
+      </c>
+      <c r="K98" t="s">
+        <v>410</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="99" spans="4:13">
+      <c r="D99" t="s">
+        <v>112</v>
+      </c>
+      <c r="F99" t="s">
+        <v>211</v>
+      </c>
+      <c r="G99" t="s">
+        <v>211</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I99" t="s">
+        <v>408</v>
+      </c>
+      <c r="J99" t="s">
+        <v>409</v>
+      </c>
+      <c r="K99" t="s">
+        <v>410</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="100" spans="4:13">
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="F100" t="s">
+        <v>211</v>
+      </c>
+      <c r="G100" t="s">
+        <v>211</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I100" t="s">
+        <v>408</v>
+      </c>
+      <c r="J100" t="s">
+        <v>409</v>
+      </c>
+      <c r="K100" t="s">
+        <v>410</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="101" spans="4:13">
+      <c r="D101" t="s">
+        <v>114</v>
+      </c>
+      <c r="F101" t="s">
+        <v>211</v>
+      </c>
+      <c r="G101" t="s">
+        <v>211</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I101" t="s">
+        <v>408</v>
+      </c>
+      <c r="J101" t="s">
+        <v>409</v>
+      </c>
+      <c r="K101" t="s">
+        <v>410</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="102" spans="4:13">
+      <c r="D102" t="s">
+        <v>115</v>
+      </c>
+      <c r="F102" t="s">
+        <v>211</v>
+      </c>
+      <c r="G102" t="s">
+        <v>211</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I102" t="s">
+        <v>408</v>
+      </c>
+      <c r="J102" t="s">
+        <v>409</v>
+      </c>
+      <c r="K102" t="s">
+        <v>410</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="103" spans="4:13">
+      <c r="D103" t="s">
+        <v>116</v>
+      </c>
+      <c r="F103" t="s">
+        <v>211</v>
+      </c>
+      <c r="G103" t="s">
+        <v>211</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I103" t="s">
+        <v>408</v>
+      </c>
+      <c r="J103" t="s">
+        <v>409</v>
+      </c>
+      <c r="K103" t="s">
+        <v>410</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="104" spans="4:13">
+      <c r="D104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" t="s">
+        <v>211</v>
+      </c>
+      <c r="G104" t="s">
+        <v>211</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I104" t="s">
+        <v>408</v>
+      </c>
+      <c r="J104" t="s">
+        <v>409</v>
+      </c>
+      <c r="K104" t="s">
+        <v>410</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="105" spans="4:13">
+      <c r="D105" t="s">
+        <v>118</v>
+      </c>
+      <c r="F105" t="s">
+        <v>211</v>
+      </c>
+      <c r="G105" t="s">
+        <v>211</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I105" t="s">
+        <v>408</v>
+      </c>
+      <c r="J105" t="s">
+        <v>409</v>
+      </c>
+      <c r="K105" t="s">
+        <v>410</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="106" spans="4:13">
+      <c r="D106" t="s">
+        <v>119</v>
+      </c>
+      <c r="F106" t="s">
+        <v>211</v>
+      </c>
+      <c r="G106" t="s">
+        <v>211</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I106" t="s">
+        <v>408</v>
+      </c>
+      <c r="J106" t="s">
+        <v>409</v>
+      </c>
+      <c r="K106" t="s">
+        <v>410</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="107" spans="4:13">
+      <c r="D107" t="s">
+        <v>120</v>
+      </c>
+      <c r="F107" t="s">
+        <v>211</v>
+      </c>
+      <c r="G107" t="s">
+        <v>211</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I107" t="s">
+        <v>408</v>
+      </c>
+      <c r="J107" t="s">
+        <v>409</v>
+      </c>
+      <c r="K107" t="s">
+        <v>410</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="108" spans="4:13">
+      <c r="D108" t="s">
+        <v>121</v>
+      </c>
+      <c r="F108" t="s">
+        <v>211</v>
+      </c>
+      <c r="G108" t="s">
+        <v>211</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I108" t="s">
+        <v>408</v>
+      </c>
+      <c r="J108" t="s">
+        <v>409</v>
+      </c>
+      <c r="K108" t="s">
+        <v>410</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="109" spans="4:13">
+      <c r="D109" t="s">
+        <v>122</v>
+      </c>
+      <c r="F109" t="s">
+        <v>211</v>
+      </c>
+      <c r="G109" t="s">
+        <v>211</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I109" t="s">
+        <v>408</v>
+      </c>
+      <c r="J109" t="s">
+        <v>409</v>
+      </c>
+      <c r="K109" t="s">
+        <v>410</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="110" spans="4:13">
+      <c r="D110" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" t="s">
+        <v>211</v>
+      </c>
+      <c r="G110" t="s">
+        <v>211</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I110" t="s">
+        <v>408</v>
+      </c>
+      <c r="J110" t="s">
+        <v>409</v>
+      </c>
+      <c r="K110" t="s">
+        <v>410</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="111" spans="4:13">
+      <c r="D111" t="s">
+        <v>124</v>
+      </c>
+      <c r="F111" t="s">
+        <v>211</v>
+      </c>
+      <c r="G111" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I111" t="s">
+        <v>408</v>
+      </c>
+      <c r="J111" t="s">
+        <v>409</v>
+      </c>
+      <c r="K111" t="s">
+        <v>410</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="112" spans="4:13">
+      <c r="D112" t="s">
+        <v>125</v>
+      </c>
+      <c r="F112" t="s">
+        <v>211</v>
+      </c>
+      <c r="G112" t="s">
+        <v>211</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I112" t="s">
+        <v>408</v>
+      </c>
+      <c r="J112" t="s">
+        <v>409</v>
+      </c>
+      <c r="K112" t="s">
+        <v>410</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="113" spans="4:13">
+      <c r="D113" t="s">
+        <v>126</v>
+      </c>
+      <c r="F113" t="s">
+        <v>211</v>
+      </c>
+      <c r="G113" t="s">
+        <v>211</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I113" t="s">
+        <v>408</v>
+      </c>
+      <c r="J113" t="s">
+        <v>409</v>
+      </c>
+      <c r="K113" t="s">
+        <v>410</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="114" spans="4:13">
+      <c r="D114" t="s">
+        <v>127</v>
+      </c>
+      <c r="F114" t="s">
+        <v>211</v>
+      </c>
+      <c r="G114" t="s">
+        <v>211</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I114" t="s">
+        <v>408</v>
+      </c>
+      <c r="J114" t="s">
+        <v>409</v>
+      </c>
+      <c r="K114" t="s">
+        <v>410</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="115" spans="4:13">
+      <c r="D115" t="s">
+        <v>128</v>
+      </c>
+      <c r="F115" t="s">
+        <v>211</v>
+      </c>
+      <c r="G115" t="s">
+        <v>211</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I115" t="s">
+        <v>408</v>
+      </c>
+      <c r="J115" t="s">
+        <v>409</v>
+      </c>
+      <c r="K115" t="s">
+        <v>410</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="116" spans="4:13">
+      <c r="D116" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" t="s">
+        <v>211</v>
+      </c>
+      <c r="G116" t="s">
+        <v>211</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I116" t="s">
+        <v>408</v>
+      </c>
+      <c r="J116" t="s">
+        <v>409</v>
+      </c>
+      <c r="K116" t="s">
+        <v>410</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="117" spans="4:13">
+      <c r="D117" t="s">
+        <v>130</v>
+      </c>
+      <c r="F117" t="s">
+        <v>211</v>
+      </c>
+      <c r="G117" t="s">
+        <v>211</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I117" t="s">
+        <v>408</v>
+      </c>
+      <c r="J117" t="s">
+        <v>409</v>
+      </c>
+      <c r="K117" t="s">
+        <v>410</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="118" spans="4:13">
+      <c r="D118" t="s">
+        <v>131</v>
+      </c>
+      <c r="F118" t="s">
+        <v>211</v>
+      </c>
+      <c r="G118" t="s">
+        <v>211</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I118" t="s">
+        <v>408</v>
+      </c>
+      <c r="J118" t="s">
+        <v>409</v>
+      </c>
+      <c r="K118" t="s">
+        <v>410</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="119" spans="4:13">
+      <c r="D119" t="s">
+        <v>132</v>
+      </c>
+      <c r="F119" t="s">
+        <v>211</v>
+      </c>
+      <c r="G119" t="s">
+        <v>211</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I119" t="s">
+        <v>408</v>
+      </c>
+      <c r="J119" t="s">
+        <v>409</v>
+      </c>
+      <c r="K119" t="s">
+        <v>410</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="120" spans="4:13">
+      <c r="D120" t="s">
+        <v>133</v>
+      </c>
+      <c r="F120" t="s">
+        <v>211</v>
+      </c>
+      <c r="G120" t="s">
+        <v>211</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="I120" t="s">
+        <v>408</v>
+      </c>
+      <c r="J120" t="s">
+        <v>409</v>
+      </c>
+      <c r="K120" t="s">
+        <v>410</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="121" spans="4:13">
+      <c r="D121" t="s">
+        <v>134</v>
+      </c>
+      <c r="F121" t="s">
+        <v>211</v>
+      </c>
+      <c r="G121" t="s">
+        <v>211</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="I121" t="s">
+        <v>408</v>
+      </c>
+      <c r="J121" t="s">
+        <v>409</v>
+      </c>
+      <c r="K121" t="s">
+        <v>410</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="122" spans="4:13">
+      <c r="D122" t="s">
+        <v>135</v>
+      </c>
+      <c r="F122" t="s">
+        <v>211</v>
+      </c>
+      <c r="G122" t="s">
+        <v>211</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I122" t="s">
+        <v>408</v>
+      </c>
+      <c r="J122" t="s">
+        <v>409</v>
+      </c>
+      <c r="K122" t="s">
+        <v>410</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="123" spans="4:13">
+      <c r="D123" t="s">
+        <v>136</v>
+      </c>
+      <c r="F123" t="s">
+        <v>211</v>
+      </c>
+      <c r="G123" t="s">
+        <v>211</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I123" t="s">
+        <v>408</v>
+      </c>
+      <c r="J123" t="s">
+        <v>409</v>
+      </c>
+      <c r="K123" t="s">
+        <v>410</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="124" spans="4:13">
+      <c r="D124" t="s">
+        <v>137</v>
+      </c>
+      <c r="F124" t="s">
+        <v>211</v>
+      </c>
+      <c r="G124" t="s">
+        <v>211</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I124" t="s">
+        <v>408</v>
+      </c>
+      <c r="J124" t="s">
+        <v>409</v>
+      </c>
+      <c r="K124" t="s">
+        <v>410</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="125" spans="4:13">
+      <c r="D125" t="s">
+        <v>138</v>
+      </c>
+      <c r="F125" t="s">
+        <v>211</v>
+      </c>
+      <c r="G125" t="s">
+        <v>211</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I125" t="s">
+        <v>408</v>
+      </c>
+      <c r="J125" t="s">
+        <v>409</v>
+      </c>
+      <c r="K125" t="s">
+        <v>410</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="126" spans="4:13">
+      <c r="D126" t="s">
+        <v>139</v>
+      </c>
+      <c r="F126" t="s">
+        <v>211</v>
+      </c>
+      <c r="G126" t="s">
+        <v>211</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I126" t="s">
+        <v>408</v>
+      </c>
+      <c r="J126" t="s">
+        <v>409</v>
+      </c>
+      <c r="K126" t="s">
+        <v>410</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="127" spans="4:13">
+      <c r="D127" t="s">
+        <v>140</v>
+      </c>
+      <c r="F127" t="s">
+        <v>211</v>
+      </c>
+      <c r="G127" t="s">
+        <v>211</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I127" t="s">
+        <v>408</v>
+      </c>
+      <c r="J127" t="s">
+        <v>409</v>
+      </c>
+      <c r="K127" t="s">
+        <v>410</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="128" spans="4:13">
+      <c r="D128" t="s">
+        <v>141</v>
+      </c>
+      <c r="F128" t="s">
+        <v>211</v>
+      </c>
+      <c r="G128" t="s">
+        <v>211</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I128" t="s">
+        <v>408</v>
+      </c>
+      <c r="J128" t="s">
+        <v>409</v>
+      </c>
+      <c r="K128" t="s">
+        <v>410</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="129" spans="4:13">
+      <c r="D129" t="s">
+        <v>142</v>
+      </c>
+      <c r="F129" t="s">
+        <v>211</v>
+      </c>
+      <c r="G129" t="s">
+        <v>211</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I129" t="s">
+        <v>408</v>
+      </c>
+      <c r="J129" t="s">
+        <v>409</v>
+      </c>
+      <c r="K129" t="s">
+        <v>410</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="130" spans="4:13">
+      <c r="D130" t="s">
+        <v>143</v>
+      </c>
+      <c r="F130" t="s">
+        <v>211</v>
+      </c>
+      <c r="G130" t="s">
+        <v>211</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I130" t="s">
+        <v>408</v>
+      </c>
+      <c r="J130" t="s">
+        <v>409</v>
+      </c>
+      <c r="K130" t="s">
+        <v>410</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="131" spans="4:13">
+      <c r="D131" t="s">
+        <v>144</v>
+      </c>
+      <c r="F131" t="s">
+        <v>211</v>
+      </c>
+      <c r="G131" t="s">
+        <v>211</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I131" t="s">
+        <v>408</v>
+      </c>
+      <c r="J131" t="s">
+        <v>409</v>
+      </c>
+      <c r="K131" t="s">
+        <v>410</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="132" spans="4:13">
+      <c r="D132" t="s">
+        <v>145</v>
+      </c>
+      <c r="F132" t="s">
+        <v>211</v>
+      </c>
+      <c r="G132" t="s">
+        <v>211</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I132" t="s">
+        <v>408</v>
+      </c>
+      <c r="J132" t="s">
+        <v>409</v>
+      </c>
+      <c r="K132" t="s">
+        <v>410</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="133" spans="4:13">
+      <c r="D133" t="s">
+        <v>146</v>
+      </c>
+      <c r="F133" t="s">
+        <v>211</v>
+      </c>
+      <c r="G133" t="s">
+        <v>211</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I133" t="s">
+        <v>408</v>
+      </c>
+      <c r="J133" t="s">
+        <v>409</v>
+      </c>
+      <c r="K133" t="s">
+        <v>410</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="134" spans="4:13">
+      <c r="D134" t="s">
+        <v>147</v>
+      </c>
+      <c r="F134" t="s">
+        <v>211</v>
+      </c>
+      <c r="G134" t="s">
+        <v>211</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I134" t="s">
+        <v>408</v>
+      </c>
+      <c r="J134" t="s">
+        <v>409</v>
+      </c>
+      <c r="K134" t="s">
+        <v>410</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="135" spans="4:13">
+      <c r="D135" t="s">
+        <v>148</v>
+      </c>
+      <c r="F135" t="s">
+        <v>211</v>
+      </c>
+      <c r="G135" t="s">
+        <v>211</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I135" t="s">
+        <v>408</v>
+      </c>
+      <c r="J135" t="s">
+        <v>409</v>
+      </c>
+      <c r="K135" t="s">
+        <v>410</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="136" spans="4:13">
+      <c r="D136" t="s">
+        <v>149</v>
+      </c>
+      <c r="F136" t="s">
+        <v>211</v>
+      </c>
+      <c r="G136" t="s">
+        <v>211</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I136" t="s">
+        <v>408</v>
+      </c>
+      <c r="J136" t="s">
+        <v>409</v>
+      </c>
+      <c r="K136" t="s">
+        <v>410</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="137" spans="4:13">
+      <c r="D137" t="s">
+        <v>150</v>
+      </c>
+      <c r="F137" t="s">
+        <v>211</v>
+      </c>
+      <c r="G137" t="s">
+        <v>211</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I137" t="s">
+        <v>408</v>
+      </c>
+      <c r="J137" t="s">
+        <v>409</v>
+      </c>
+      <c r="K137" t="s">
+        <v>410</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="138" spans="4:13">
+      <c r="D138" t="s">
+        <v>151</v>
+      </c>
+      <c r="F138" t="s">
+        <v>211</v>
+      </c>
+      <c r="G138" t="s">
+        <v>211</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I138" t="s">
+        <v>408</v>
+      </c>
+      <c r="J138" t="s">
+        <v>409</v>
+      </c>
+      <c r="K138" t="s">
+        <v>410</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="139" spans="4:13">
+      <c r="D139" t="s">
+        <v>152</v>
+      </c>
+      <c r="F139" t="s">
+        <v>211</v>
+      </c>
+      <c r="G139" t="s">
+        <v>211</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I139" t="s">
+        <v>408</v>
+      </c>
+      <c r="J139" t="s">
+        <v>409</v>
+      </c>
+      <c r="K139" t="s">
+        <v>410</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="140" spans="4:13">
+      <c r="D140" t="s">
+        <v>153</v>
+      </c>
+      <c r="F140" t="s">
+        <v>211</v>
+      </c>
+      <c r="G140" t="s">
+        <v>211</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I140" t="s">
+        <v>408</v>
+      </c>
+      <c r="J140" t="s">
+        <v>409</v>
+      </c>
+      <c r="K140" t="s">
+        <v>410</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="141" spans="4:13">
+      <c r="D141" t="s">
+        <v>154</v>
+      </c>
+      <c r="F141" t="s">
+        <v>211</v>
+      </c>
+      <c r="G141" t="s">
+        <v>211</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I141" t="s">
+        <v>408</v>
+      </c>
+      <c r="J141" t="s">
+        <v>409</v>
+      </c>
+      <c r="K141" t="s">
+        <v>410</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="142" spans="4:13">
+      <c r="D142" t="s">
+        <v>155</v>
+      </c>
+      <c r="F142" t="s">
+        <v>211</v>
+      </c>
+      <c r="G142" t="s">
+        <v>211</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I142" t="s">
+        <v>408</v>
+      </c>
+      <c r="J142" t="s">
+        <v>409</v>
+      </c>
+      <c r="K142" t="s">
+        <v>410</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="143" spans="4:13">
+      <c r="D143" t="s">
+        <v>156</v>
+      </c>
+      <c r="F143" t="s">
+        <v>211</v>
+      </c>
+      <c r="G143" t="s">
+        <v>211</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I143" t="s">
+        <v>408</v>
+      </c>
+      <c r="J143" t="s">
+        <v>409</v>
+      </c>
+      <c r="K143" t="s">
+        <v>410</v>
+      </c>
+      <c r="M143" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="144" spans="4:13">
+      <c r="D144" t="s">
+        <v>157</v>
+      </c>
+      <c r="F144" t="s">
+        <v>211</v>
+      </c>
+      <c r="G144" t="s">
+        <v>211</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I144" t="s">
+        <v>408</v>
+      </c>
+      <c r="J144" t="s">
+        <v>409</v>
+      </c>
+      <c r="K144" t="s">
+        <v>410</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="145" spans="4:13">
+      <c r="D145" t="s">
+        <v>158</v>
+      </c>
+      <c r="F145" t="s">
+        <v>211</v>
+      </c>
+      <c r="G145" t="s">
+        <v>211</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I145" t="s">
+        <v>408</v>
+      </c>
+      <c r="J145" t="s">
+        <v>409</v>
+      </c>
+      <c r="K145" t="s">
+        <v>410</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="146" spans="4:13">
+      <c r="D146" t="s">
+        <v>159</v>
+      </c>
+      <c r="F146" t="s">
+        <v>211</v>
+      </c>
+      <c r="G146" t="s">
+        <v>211</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I146" t="s">
+        <v>408</v>
+      </c>
+      <c r="J146" t="s">
+        <v>409</v>
+      </c>
+      <c r="K146" t="s">
+        <v>410</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="147" spans="4:13">
+      <c r="D147" t="s">
+        <v>160</v>
+      </c>
+      <c r="F147" t="s">
+        <v>211</v>
+      </c>
+      <c r="G147" t="s">
+        <v>211</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="I147" t="s">
+        <v>408</v>
+      </c>
+      <c r="J147" t="s">
+        <v>409</v>
+      </c>
+      <c r="K147" t="s">
+        <v>410</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="148" spans="4:13">
+      <c r="D148" t="s">
+        <v>161</v>
+      </c>
+      <c r="F148" t="s">
+        <v>211</v>
+      </c>
+      <c r="G148" t="s">
+        <v>211</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I148" t="s">
+        <v>408</v>
+      </c>
+      <c r="J148" t="s">
+        <v>409</v>
+      </c>
+      <c r="K148" t="s">
+        <v>410</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="149" spans="4:13">
+      <c r="D149" t="s">
+        <v>162</v>
+      </c>
+      <c r="F149" t="s">
+        <v>211</v>
+      </c>
+      <c r="G149" t="s">
+        <v>211</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I149" t="s">
+        <v>408</v>
+      </c>
+      <c r="J149" t="s">
+        <v>409</v>
+      </c>
+      <c r="K149" t="s">
+        <v>410</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="150" spans="4:13">
+      <c r="D150" t="s">
+        <v>163</v>
+      </c>
+      <c r="F150" t="s">
+        <v>211</v>
+      </c>
+      <c r="G150" t="s">
+        <v>211</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I150" t="s">
+        <v>408</v>
+      </c>
+      <c r="J150" t="s">
+        <v>409</v>
+      </c>
+      <c r="K150" t="s">
+        <v>410</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="151" spans="4:13">
+      <c r="D151" t="s">
+        <v>164</v>
+      </c>
+      <c r="F151" t="s">
+        <v>211</v>
+      </c>
+      <c r="G151" t="s">
+        <v>211</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I151" t="s">
+        <v>408</v>
+      </c>
+      <c r="J151" t="s">
+        <v>409</v>
+      </c>
+      <c r="K151" t="s">
+        <v>410</v>
+      </c>
+      <c r="M151" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="152" spans="4:13">
+      <c r="D152" t="s">
+        <v>165</v>
+      </c>
+      <c r="F152" t="s">
+        <v>211</v>
+      </c>
+      <c r="G152" t="s">
+        <v>211</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I152" t="s">
+        <v>408</v>
+      </c>
+      <c r="J152" t="s">
+        <v>409</v>
+      </c>
+      <c r="K152" t="s">
+        <v>410</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="153" spans="4:13">
+      <c r="D153" t="s">
+        <v>166</v>
+      </c>
+      <c r="F153" t="s">
+        <v>211</v>
+      </c>
+      <c r="G153" t="s">
+        <v>211</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="I153" t="s">
+        <v>408</v>
+      </c>
+      <c r="J153" t="s">
+        <v>409</v>
+      </c>
+      <c r="K153" t="s">
+        <v>410</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="154" spans="4:13">
+      <c r="D154" t="s">
+        <v>167</v>
+      </c>
+      <c r="F154" t="s">
+        <v>211</v>
+      </c>
+      <c r="G154" t="s">
+        <v>211</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I154" t="s">
+        <v>408</v>
+      </c>
+      <c r="J154" t="s">
+        <v>409</v>
+      </c>
+      <c r="K154" t="s">
+        <v>410</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="155" spans="4:13">
+      <c r="D155" t="s">
+        <v>168</v>
+      </c>
+      <c r="F155" t="s">
+        <v>211</v>
+      </c>
+      <c r="G155" t="s">
+        <v>211</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I155" t="s">
+        <v>408</v>
+      </c>
+      <c r="J155" t="s">
+        <v>409</v>
+      </c>
+      <c r="K155" t="s">
+        <v>410</v>
+      </c>
+      <c r="M155" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="156" spans="4:13">
+      <c r="D156" t="s">
+        <v>169</v>
+      </c>
+      <c r="F156" t="s">
+        <v>211</v>
+      </c>
+      <c r="G156" t="s">
+        <v>211</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="I156" t="s">
+        <v>408</v>
+      </c>
+      <c r="J156" t="s">
+        <v>409</v>
+      </c>
+      <c r="K156" t="s">
+        <v>410</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="157" spans="4:13">
+      <c r="D157" t="s">
+        <v>170</v>
+      </c>
+      <c r="F157" t="s">
+        <v>211</v>
+      </c>
+      <c r="G157" t="s">
+        <v>211</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I157" t="s">
+        <v>408</v>
+      </c>
+      <c r="J157" t="s">
+        <v>409</v>
+      </c>
+      <c r="K157" t="s">
+        <v>410</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="158" spans="4:13">
+      <c r="D158" t="s">
+        <v>171</v>
+      </c>
+      <c r="F158" t="s">
+        <v>211</v>
+      </c>
+      <c r="G158" t="s">
+        <v>211</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="I158" t="s">
+        <v>408</v>
+      </c>
+      <c r="J158" t="s">
+        <v>409</v>
+      </c>
+      <c r="K158" t="s">
+        <v>410</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="159" spans="4:13">
+      <c r="D159" t="s">
+        <v>172</v>
+      </c>
+      <c r="F159" t="s">
+        <v>211</v>
+      </c>
+      <c r="G159" t="s">
+        <v>211</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="I159" t="s">
+        <v>408</v>
+      </c>
+      <c r="J159" t="s">
+        <v>409</v>
+      </c>
+      <c r="K159" t="s">
+        <v>410</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="160" spans="4:13">
+      <c r="D160" t="s">
+        <v>173</v>
+      </c>
+      <c r="F160" t="s">
+        <v>211</v>
+      </c>
+      <c r="G160" t="s">
+        <v>211</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="I160" t="s">
+        <v>408</v>
+      </c>
+      <c r="J160" t="s">
+        <v>409</v>
+      </c>
+      <c r="K160" t="s">
+        <v>410</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="161" spans="4:13">
+      <c r="D161" t="s">
+        <v>174</v>
+      </c>
+      <c r="F161" t="s">
+        <v>211</v>
+      </c>
+      <c r="G161" t="s">
+        <v>211</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I161" t="s">
+        <v>408</v>
+      </c>
+      <c r="J161" t="s">
+        <v>409</v>
+      </c>
+      <c r="K161" t="s">
+        <v>410</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="162" spans="4:13">
+      <c r="D162" t="s">
+        <v>175</v>
+      </c>
+      <c r="F162" t="s">
+        <v>211</v>
+      </c>
+      <c r="G162" t="s">
+        <v>211</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I162" t="s">
+        <v>408</v>
+      </c>
+      <c r="J162" t="s">
+        <v>409</v>
+      </c>
+      <c r="K162" t="s">
+        <v>410</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="163" spans="4:13">
+      <c r="D163" t="s">
+        <v>176</v>
+      </c>
+      <c r="F163" t="s">
+        <v>211</v>
+      </c>
+      <c r="G163" t="s">
+        <v>211</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I163" t="s">
+        <v>408</v>
+      </c>
+      <c r="J163" t="s">
+        <v>409</v>
+      </c>
+      <c r="K163" t="s">
+        <v>410</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="164" spans="4:13">
+      <c r="D164" t="s">
+        <v>177</v>
+      </c>
+      <c r="F164" t="s">
+        <v>211</v>
+      </c>
+      <c r="G164" t="s">
+        <v>211</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I164" t="s">
+        <v>408</v>
+      </c>
+      <c r="J164" t="s">
+        <v>409</v>
+      </c>
+      <c r="K164" t="s">
+        <v>410</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="165" spans="4:13">
+      <c r="D165" t="s">
+        <v>178</v>
+      </c>
+      <c r="F165" t="s">
+        <v>211</v>
+      </c>
+      <c r="G165" t="s">
+        <v>211</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I165" t="s">
+        <v>408</v>
+      </c>
+      <c r="J165" t="s">
+        <v>409</v>
+      </c>
+      <c r="K165" t="s">
+        <v>410</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="166" spans="4:13">
+      <c r="D166" t="s">
+        <v>179</v>
+      </c>
+      <c r="F166" t="s">
+        <v>211</v>
+      </c>
+      <c r="G166" t="s">
+        <v>211</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I166" t="s">
+        <v>408</v>
+      </c>
+      <c r="J166" t="s">
+        <v>409</v>
+      </c>
+      <c r="K166" t="s">
+        <v>410</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="167" spans="4:13">
+      <c r="D167" t="s">
+        <v>180</v>
+      </c>
+      <c r="F167" t="s">
+        <v>211</v>
+      </c>
+      <c r="G167" t="s">
+        <v>211</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I167" t="s">
+        <v>408</v>
+      </c>
+      <c r="J167" t="s">
+        <v>409</v>
+      </c>
+      <c r="K167" t="s">
+        <v>410</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="168" spans="4:13">
+      <c r="D168" t="s">
+        <v>181</v>
+      </c>
+      <c r="F168" t="s">
+        <v>211</v>
+      </c>
+      <c r="G168" t="s">
+        <v>211</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I168" t="s">
+        <v>408</v>
+      </c>
+      <c r="J168" t="s">
+        <v>409</v>
+      </c>
+      <c r="K168" t="s">
+        <v>410</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="169" spans="4:13">
+      <c r="D169" t="s">
+        <v>182</v>
+      </c>
+      <c r="F169" t="s">
+        <v>211</v>
+      </c>
+      <c r="G169" t="s">
+        <v>211</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I169" t="s">
+        <v>408</v>
+      </c>
+      <c r="J169" t="s">
+        <v>409</v>
+      </c>
+      <c r="K169" t="s">
+        <v>410</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="170" spans="4:13">
+      <c r="D170" t="s">
+        <v>183</v>
+      </c>
+      <c r="F170" t="s">
+        <v>211</v>
+      </c>
+      <c r="G170" t="s">
+        <v>211</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I170" t="s">
+        <v>408</v>
+      </c>
+      <c r="J170" t="s">
+        <v>409</v>
+      </c>
+      <c r="K170" t="s">
+        <v>410</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="171" spans="4:13">
+      <c r="D171" t="s">
+        <v>184</v>
+      </c>
+      <c r="F171" t="s">
+        <v>211</v>
+      </c>
+      <c r="G171" t="s">
+        <v>211</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I171" t="s">
+        <v>408</v>
+      </c>
+      <c r="J171" t="s">
+        <v>409</v>
+      </c>
+      <c r="K171" t="s">
+        <v>410</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="172" spans="4:13">
+      <c r="D172" t="s">
+        <v>185</v>
+      </c>
+      <c r="F172" t="s">
+        <v>211</v>
+      </c>
+      <c r="G172" t="s">
+        <v>211</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I172" t="s">
+        <v>408</v>
+      </c>
+      <c r="J172" t="s">
+        <v>409</v>
+      </c>
+      <c r="K172" t="s">
+        <v>410</v>
+      </c>
+      <c r="M172" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="173" spans="4:13">
+      <c r="D173" t="s">
+        <v>186</v>
+      </c>
+      <c r="F173" t="s">
+        <v>211</v>
+      </c>
+      <c r="G173" t="s">
+        <v>211</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I173" t="s">
+        <v>408</v>
+      </c>
+      <c r="J173" t="s">
+        <v>409</v>
+      </c>
+      <c r="K173" t="s">
+        <v>410</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="174" spans="4:13">
+      <c r="D174" t="s">
+        <v>187</v>
+      </c>
+      <c r="F174" t="s">
+        <v>211</v>
+      </c>
+      <c r="G174" t="s">
+        <v>211</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I174" t="s">
+        <v>408</v>
+      </c>
+      <c r="J174" t="s">
+        <v>409</v>
+      </c>
+      <c r="K174" t="s">
+        <v>410</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="175" spans="4:13">
+      <c r="D175" t="s">
+        <v>188</v>
+      </c>
+      <c r="F175" t="s">
+        <v>211</v>
+      </c>
+      <c r="G175" t="s">
+        <v>211</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I175" t="s">
+        <v>408</v>
+      </c>
+      <c r="J175" t="s">
+        <v>409</v>
+      </c>
+      <c r="K175" t="s">
+        <v>410</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="176" spans="4:13">
+      <c r="D176" t="s">
+        <v>189</v>
+      </c>
+      <c r="F176" t="s">
+        <v>211</v>
+      </c>
+      <c r="G176" t="s">
+        <v>211</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I176" t="s">
+        <v>408</v>
+      </c>
+      <c r="J176" t="s">
+        <v>409</v>
+      </c>
+      <c r="K176" t="s">
+        <v>410</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="177" spans="4:13">
+      <c r="D177" t="s">
+        <v>190</v>
+      </c>
+      <c r="F177" t="s">
+        <v>211</v>
+      </c>
+      <c r="G177" t="s">
+        <v>211</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I177" t="s">
+        <v>408</v>
+      </c>
+      <c r="J177" t="s">
+        <v>409</v>
+      </c>
+      <c r="K177" t="s">
+        <v>410</v>
+      </c>
+      <c r="M177" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="178" spans="4:13">
+      <c r="D178" t="s">
+        <v>191</v>
+      </c>
+      <c r="F178" t="s">
+        <v>211</v>
+      </c>
+      <c r="G178" t="s">
+        <v>211</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I178" t="s">
+        <v>408</v>
+      </c>
+      <c r="J178" t="s">
+        <v>409</v>
+      </c>
+      <c r="K178" t="s">
+        <v>410</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="179" spans="4:13">
+      <c r="D179" t="s">
+        <v>192</v>
+      </c>
+      <c r="F179" t="s">
+        <v>211</v>
+      </c>
+      <c r="G179" t="s">
+        <v>211</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I179" t="s">
+        <v>408</v>
+      </c>
+      <c r="J179" t="s">
+        <v>409</v>
+      </c>
+      <c r="K179" t="s">
+        <v>410</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="180" spans="4:13">
+      <c r="D180" t="s">
+        <v>193</v>
+      </c>
+      <c r="F180" t="s">
+        <v>211</v>
+      </c>
+      <c r="G180" t="s">
+        <v>211</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="I180" t="s">
+        <v>408</v>
+      </c>
+      <c r="J180" t="s">
+        <v>409</v>
+      </c>
+      <c r="K180" t="s">
+        <v>410</v>
+      </c>
+      <c r="M180" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="181" spans="4:13">
+      <c r="D181" t="s">
+        <v>194</v>
+      </c>
+      <c r="F181" t="s">
+        <v>211</v>
+      </c>
+      <c r="G181" t="s">
+        <v>211</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I181" t="s">
+        <v>408</v>
+      </c>
+      <c r="J181" t="s">
+        <v>409</v>
+      </c>
+      <c r="K181" t="s">
+        <v>410</v>
+      </c>
+      <c r="M181" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="182" spans="4:13">
+      <c r="D182" t="s">
+        <v>195</v>
+      </c>
+      <c r="F182" t="s">
+        <v>211</v>
+      </c>
+      <c r="G182" t="s">
+        <v>211</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I182" t="s">
+        <v>408</v>
+      </c>
+      <c r="J182" t="s">
+        <v>409</v>
+      </c>
+      <c r="K182" t="s">
+        <v>410</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="183" spans="4:13">
+      <c r="D183" t="s">
+        <v>196</v>
+      </c>
+      <c r="F183" t="s">
+        <v>211</v>
+      </c>
+      <c r="G183" t="s">
+        <v>211</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I183" t="s">
+        <v>408</v>
+      </c>
+      <c r="J183" t="s">
+        <v>409</v>
+      </c>
+      <c r="K183" t="s">
+        <v>410</v>
+      </c>
+      <c r="M183" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="184" spans="4:13">
+      <c r="D184" t="s">
+        <v>197</v>
+      </c>
+      <c r="F184" t="s">
+        <v>211</v>
+      </c>
+      <c r="G184" t="s">
+        <v>211</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I184" t="s">
+        <v>408</v>
+      </c>
+      <c r="J184" t="s">
+        <v>409</v>
+      </c>
+      <c r="K184" t="s">
+        <v>410</v>
+      </c>
+      <c r="M184" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="185" spans="4:13">
+      <c r="D185" t="s">
+        <v>198</v>
+      </c>
+      <c r="F185" t="s">
+        <v>211</v>
+      </c>
+      <c r="G185" t="s">
+        <v>211</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I185" t="s">
+        <v>408</v>
+      </c>
+      <c r="J185" t="s">
+        <v>409</v>
+      </c>
+      <c r="K185" t="s">
+        <v>410</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="186" spans="4:13">
+      <c r="D186" t="s">
+        <v>199</v>
+      </c>
+      <c r="F186" t="s">
+        <v>211</v>
+      </c>
+      <c r="G186" t="s">
+        <v>211</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I186" t="s">
+        <v>408</v>
+      </c>
+      <c r="J186" t="s">
+        <v>409</v>
+      </c>
+      <c r="K186" t="s">
+        <v>410</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="187" spans="4:13">
+      <c r="D187" t="s">
+        <v>200</v>
+      </c>
+      <c r="F187" t="s">
+        <v>211</v>
+      </c>
+      <c r="G187" t="s">
+        <v>211</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I187" t="s">
+        <v>408</v>
+      </c>
+      <c r="J187" t="s">
+        <v>409</v>
+      </c>
+      <c r="K187" t="s">
+        <v>410</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="188" spans="4:13">
+      <c r="D188" t="s">
+        <v>201</v>
+      </c>
+      <c r="F188" t="s">
+        <v>211</v>
+      </c>
+      <c r="G188" t="s">
+        <v>211</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I188" t="s">
+        <v>408</v>
+      </c>
+      <c r="J188" t="s">
+        <v>409</v>
+      </c>
+      <c r="K188" t="s">
+        <v>410</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="189" spans="4:13">
+      <c r="D189" t="s">
+        <v>202</v>
+      </c>
+      <c r="F189" t="s">
+        <v>211</v>
+      </c>
+      <c r="G189" t="s">
+        <v>211</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I189" t="s">
+        <v>408</v>
+      </c>
+      <c r="J189" t="s">
+        <v>409</v>
+      </c>
+      <c r="K189" t="s">
+        <v>410</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="190" spans="4:13">
+      <c r="D190" t="s">
+        <v>203</v>
+      </c>
+      <c r="F190" t="s">
+        <v>211</v>
+      </c>
+      <c r="G190" t="s">
+        <v>211</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I190" t="s">
+        <v>408</v>
+      </c>
+      <c r="J190" t="s">
+        <v>409</v>
+      </c>
+      <c r="K190" t="s">
+        <v>410</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="191" spans="4:13">
+      <c r="D191" t="s">
+        <v>204</v>
+      </c>
+      <c r="F191" t="s">
+        <v>211</v>
+      </c>
+      <c r="G191" t="s">
+        <v>211</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I191" t="s">
+        <v>408</v>
+      </c>
+      <c r="J191" t="s">
+        <v>409</v>
+      </c>
+      <c r="K191" t="s">
+        <v>410</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="192" spans="4:13">
+      <c r="D192" t="s">
+        <v>205</v>
+      </c>
+      <c r="F192" t="s">
+        <v>211</v>
+      </c>
+      <c r="G192" t="s">
+        <v>211</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I192" t="s">
+        <v>408</v>
+      </c>
+      <c r="J192" t="s">
+        <v>409</v>
+      </c>
+      <c r="K192" t="s">
+        <v>410</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="193" spans="4:13">
+      <c r="D193" t="s">
+        <v>206</v>
+      </c>
+      <c r="F193" t="s">
+        <v>211</v>
+      </c>
+      <c r="G193" t="s">
+        <v>211</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I193" t="s">
+        <v>408</v>
+      </c>
+      <c r="J193" t="s">
+        <v>409</v>
+      </c>
+      <c r="K193" t="s">
+        <v>410</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="194" spans="4:13">
+      <c r="D194" t="s">
+        <v>207</v>
+      </c>
+      <c r="F194" t="s">
+        <v>211</v>
+      </c>
+      <c r="G194" t="s">
+        <v>211</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I194" t="s">
+        <v>408</v>
+      </c>
+      <c r="J194" t="s">
+        <v>409</v>
+      </c>
+      <c r="K194" t="s">
+        <v>410</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="195" spans="4:13">
+      <c r="D195" t="s">
+        <v>208</v>
+      </c>
+      <c r="F195" t="s">
+        <v>211</v>
+      </c>
+      <c r="G195" t="s">
+        <v>211</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I195" t="s">
+        <v>408</v>
+      </c>
+      <c r="J195" t="s">
+        <v>409</v>
+      </c>
+      <c r="K195" t="s">
+        <v>410</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="196" spans="4:13">
+      <c r="D196" t="s">
+        <v>209</v>
+      </c>
+      <c r="F196" t="s">
+        <v>211</v>
+      </c>
+      <c r="G196" t="s">
+        <v>211</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I196" t="s">
+        <v>408</v>
+      </c>
+      <c r="J196" t="s">
+        <v>409</v>
+      </c>
+      <c r="K196" t="s">
+        <v>410</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="197" spans="4:13">
+      <c r="D197" t="s">
+        <v>210</v>
+      </c>
+      <c r="F197" t="s">
+        <v>211</v>
+      </c>
+      <c r="G197" t="s">
+        <v>211</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I197" t="s">
+        <v>408</v>
+      </c>
+      <c r="J197" t="s">
+        <v>409</v>
+      </c>
+      <c r="K197" t="s">
+        <v>410</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -1127,6 +7427,366 @@
     <hyperlink ref="M16" r:id="rId30" location="region=0500000US39159"/>
     <hyperlink ref="H17" r:id="rId31"/>
     <hyperlink ref="M17" r:id="rId32" location="region=M010000US001"/>
+    <hyperlink ref="H18" r:id="rId33"/>
+    <hyperlink ref="M18" r:id="rId34" location="region=M100000US3902680"/>
+    <hyperlink ref="H19" r:id="rId35"/>
+    <hyperlink ref="M19" r:id="rId36" location="region=M100000US3903758"/>
+    <hyperlink ref="H20" r:id="rId37"/>
+    <hyperlink ref="M20" r:id="rId38" location="region=M100000US390410577499999"/>
+    <hyperlink ref="H21" r:id="rId39"/>
+    <hyperlink ref="M21" r:id="rId40" location="region=M100000US390410578899999"/>
+    <hyperlink ref="H22" r:id="rId41"/>
+    <hyperlink ref="M22" r:id="rId42" location="region=M100000US390411814099999"/>
+    <hyperlink ref="H23" r:id="rId43"/>
+    <hyperlink ref="M23" r:id="rId44" location="region=M100000US390412144899999"/>
+    <hyperlink ref="H24" r:id="rId45"/>
+    <hyperlink ref="M24" r:id="rId46" location="region=M100000US390412969499999"/>
+    <hyperlink ref="H25" r:id="rId47"/>
+    <hyperlink ref="M25" r:id="rId48" location="region=M100000US390413351699999"/>
+    <hyperlink ref="H26" r:id="rId49"/>
+    <hyperlink ref="M26" r:id="rId50" location="region=M100000US390414036299999"/>
+    <hyperlink ref="H27" r:id="rId51"/>
+    <hyperlink ref="M27" r:id="rId52" location="region=M100000US390414310699999"/>
+    <hyperlink ref="H28" r:id="rId53"/>
+    <hyperlink ref="M28" r:id="rId54" location="region=M100000US390415861899999"/>
+    <hyperlink ref="H29" r:id="rId55"/>
+    <hyperlink ref="M29" r:id="rId56" location="region=M100000US390416417899999"/>
+    <hyperlink ref="H30" r:id="rId57"/>
+    <hyperlink ref="M30" r:id="rId58" location="region=M100000US390417084299999"/>
+    <hyperlink ref="H31" r:id="rId59"/>
+    <hyperlink ref="M31" r:id="rId60" location="region=M100000US390417733699999"/>
+    <hyperlink ref="H32" r:id="rId61"/>
+    <hyperlink ref="M32" r:id="rId62" location="region=M100000US390417756099999"/>
+    <hyperlink ref="H33" r:id="rId63"/>
+    <hyperlink ref="M33" r:id="rId64" location="region=M100000US390450163799999"/>
+    <hyperlink ref="H34" r:id="rId65"/>
+    <hyperlink ref="M34" r:id="rId66" location="region=M100000US390450595699999"/>
+    <hyperlink ref="H35" r:id="rId67"/>
+    <hyperlink ref="M35" r:id="rId68" location="region=M100000US390450695099999"/>
+    <hyperlink ref="H36" r:id="rId69"/>
+    <hyperlink ref="M36" r:id="rId70" location="region=M100000US390451568699999"/>
+    <hyperlink ref="H37" r:id="rId71"/>
+    <hyperlink ref="M37" r:id="rId72" location="region=M100000US390453206099999"/>
+    <hyperlink ref="H38" r:id="rId73"/>
+    <hyperlink ref="M38" r:id="rId74" location="region=M100000US390453581299999"/>
+    <hyperlink ref="H39" r:id="rId75"/>
+    <hyperlink ref="M39" r:id="rId76" location="region=M100000US390454312099999"/>
+    <hyperlink ref="H40" r:id="rId77"/>
+    <hyperlink ref="M40" r:id="rId78" location="region=M100000US390456324099999"/>
+    <hyperlink ref="H41" r:id="rId79"/>
+    <hyperlink ref="M41" r:id="rId80" location="region=M100000US390456668499999"/>
+    <hyperlink ref="H42" r:id="rId81"/>
+    <hyperlink ref="M42" r:id="rId82" location="region=M100000US390456912099999"/>
+    <hyperlink ref="H43" r:id="rId83"/>
+    <hyperlink ref="M43" r:id="rId84" location="region=M100000US390458020699999"/>
+    <hyperlink ref="H44" r:id="rId85"/>
+    <hyperlink ref="M44" r:id="rId86" location="region=M100000US390458057099999"/>
+    <hyperlink ref="H45" r:id="rId87"/>
+    <hyperlink ref="M45" r:id="rId88" location="region=M100000US390477831699999"/>
+    <hyperlink ref="H46" r:id="rId89"/>
+    <hyperlink ref="M46" r:id="rId90" location="region=M100000US390490692299999"/>
+    <hyperlink ref="H47" r:id="rId91"/>
+    <hyperlink ref="M47" r:id="rId92" location="region=M100000US390490944299999"/>
+    <hyperlink ref="H48" r:id="rId93"/>
+    <hyperlink ref="M48" r:id="rId94" location="region=M100000US390491611299999"/>
+    <hyperlink ref="H49" r:id="rId95"/>
+    <hyperlink ref="M49" r:id="rId96" location="region=M100000US390492828099999"/>
+    <hyperlink ref="H50" r:id="rId97"/>
+    <hyperlink ref="M50" r:id="rId98" location="region=M100000US390493302699999"/>
+    <hyperlink ref="H51" r:id="rId99"/>
+    <hyperlink ref="M51" r:id="rId100" location="region=M100000US390493777299999"/>
+    <hyperlink ref="H52" r:id="rId101"/>
+    <hyperlink ref="M52" r:id="rId102" location="region=M100000US390493861299999"/>
+    <hyperlink ref="H53" r:id="rId103"/>
+    <hyperlink ref="M53" r:id="rId104" location="region=M100000US390494641099999"/>
+    <hyperlink ref="H54" r:id="rId105"/>
+    <hyperlink ref="M54" r:id="rId106" location="region=M100000US390495006499999"/>
+    <hyperlink ref="H55" r:id="rId107"/>
+    <hyperlink ref="M55" r:id="rId108" location="region=M100000US390495734499999"/>
+    <hyperlink ref="H56" r:id="rId109"/>
+    <hyperlink ref="M56" r:id="rId110" location="region=M100000US390496184099999"/>
+    <hyperlink ref="H57" r:id="rId111"/>
+    <hyperlink ref="M57" r:id="rId112" location="region=M100000US390496297499999"/>
+    <hyperlink ref="H58" r:id="rId113"/>
+    <hyperlink ref="M58" r:id="rId114" location="region=M100000US390496325499999"/>
+    <hyperlink ref="H59" r:id="rId115"/>
+    <hyperlink ref="M59" r:id="rId116" location="region=M100000US390496457099999"/>
+    <hyperlink ref="H60" r:id="rId117"/>
+    <hyperlink ref="M60" r:id="rId118" location="region=M100000US390497178799999"/>
+    <hyperlink ref="H61" r:id="rId119"/>
+    <hyperlink ref="M61" r:id="rId120" location="region=M100000US390497771499999"/>
+    <hyperlink ref="H62" r:id="rId121"/>
+    <hyperlink ref="M62" r:id="rId122" location="region=M100000US390498124299999"/>
+    <hyperlink ref="H63" r:id="rId123"/>
+    <hyperlink ref="M63" r:id="rId124" location="region=M100000US3905130"/>
+    <hyperlink ref="H64" r:id="rId125"/>
+    <hyperlink ref="M64" r:id="rId126" location="region=M100000US3906278"/>
+    <hyperlink ref="H65" r:id="rId127"/>
+    <hyperlink ref="M65" r:id="rId128" location="region=M100000US390732648899999"/>
+    <hyperlink ref="H66" r:id="rId129"/>
+    <hyperlink ref="M66" r:id="rId130" location="region=M100000US390733178099999"/>
+    <hyperlink ref="H67" r:id="rId131"/>
+    <hyperlink ref="M67" r:id="rId132" location="region=M100000US390734774099999"/>
+    <hyperlink ref="H68" r:id="rId133"/>
+    <hyperlink ref="M68" r:id="rId134" location="region=M100000US390830947099999"/>
+    <hyperlink ref="H69" r:id="rId135"/>
+    <hyperlink ref="M69" r:id="rId136" location="region=M100000US390831614099999"/>
+    <hyperlink ref="H70" r:id="rId137"/>
+    <hyperlink ref="M70" r:id="rId138" location="region=M100000US390831668699999"/>
+    <hyperlink ref="H71" r:id="rId139"/>
+    <hyperlink ref="M71" r:id="rId140" location="region=M100000US390833546299999"/>
+    <hyperlink ref="H72" r:id="rId141"/>
+    <hyperlink ref="M72" r:id="rId142" location="region=M100000US390833652699999"/>
+    <hyperlink ref="H73" r:id="rId143"/>
+    <hyperlink ref="M73" r:id="rId144" location="region=M100000US390835143699999"/>
+    <hyperlink ref="H74" r:id="rId145"/>
+    <hyperlink ref="M74" r:id="rId146" location="region=M100000US390835229099999"/>
+    <hyperlink ref="H75" r:id="rId147"/>
+    <hyperlink ref="M75" r:id="rId148" location="region=M100000US390837835899999"/>
+    <hyperlink ref="H76" r:id="rId149"/>
+    <hyperlink ref="M76" r:id="rId150" location="region=M100000US390892569099999"/>
+    <hyperlink ref="H77" r:id="rId151"/>
+    <hyperlink ref="M77" r:id="rId152" location="region=M100000US390892833699999"/>
+    <hyperlink ref="H78" r:id="rId153"/>
+    <hyperlink ref="M78" r:id="rId154" location="region=M100000US390893141699999"/>
+    <hyperlink ref="H79" r:id="rId155"/>
+    <hyperlink ref="M79" r:id="rId156" location="region=M100000US390893329999999"/>
+    <hyperlink ref="H80" r:id="rId157"/>
+    <hyperlink ref="M80" r:id="rId158" location="region=M100000US390893389499999"/>
+    <hyperlink ref="H81" r:id="rId159"/>
+    <hyperlink ref="M81" r:id="rId160" location="region=M100000US390893910299999"/>
+    <hyperlink ref="H82" r:id="rId161"/>
+    <hyperlink ref="M82" r:id="rId162" location="region=M100000US390894323299999"/>
+    <hyperlink ref="H83" r:id="rId163"/>
+    <hyperlink ref="M83" r:id="rId164" location="region=M100000US390894345699999"/>
+    <hyperlink ref="H84" r:id="rId165"/>
+    <hyperlink ref="M84" r:id="rId166" location="region=M100000US390894650899999"/>
+    <hyperlink ref="H85" r:id="rId167"/>
+    <hyperlink ref="M85" r:id="rId168" location="region=M100000US390894813299999"/>
+    <hyperlink ref="H86" r:id="rId169"/>
+    <hyperlink ref="M86" r:id="rId170" location="region=M100000US390895145099999"/>
+    <hyperlink ref="H87" r:id="rId171"/>
+    <hyperlink ref="M87" r:id="rId172" location="region=M100000US390895405499999"/>
+    <hyperlink ref="H88" r:id="rId173"/>
+    <hyperlink ref="M88" r:id="rId174" location="region=M100000US390895558099999"/>
+    <hyperlink ref="H89" r:id="rId175"/>
+    <hyperlink ref="M89" r:id="rId176" location="region=M100000US390896945699999"/>
+    <hyperlink ref="H90" r:id="rId177"/>
+    <hyperlink ref="M90" r:id="rId178" location="region=M100000US390897840099999"/>
+    <hyperlink ref="H91" r:id="rId179"/>
+    <hyperlink ref="M91" r:id="rId180" location="region=M100000US390898141099999"/>
+    <hyperlink ref="H92" r:id="rId181"/>
+    <hyperlink ref="M92" r:id="rId182" location="region=M100000US390913390899999"/>
+    <hyperlink ref="H93" r:id="rId183"/>
+    <hyperlink ref="M93" r:id="rId184" location="region=M100000US390913868299999"/>
+    <hyperlink ref="H94" r:id="rId185"/>
+    <hyperlink ref="M94" r:id="rId186" location="region=M100000US390914128699999"/>
+    <hyperlink ref="H95" r:id="rId187"/>
+    <hyperlink ref="M95" r:id="rId188" location="region=M100000US390914324699999"/>
+    <hyperlink ref="H96" r:id="rId189"/>
+    <hyperlink ref="M96" r:id="rId190" location="region=M100000US390914568299999"/>
+    <hyperlink ref="H97" r:id="rId191"/>
+    <hyperlink ref="M97" r:id="rId192" location="region=M100000US390914937899999"/>
+    <hyperlink ref="H98" r:id="rId193"/>
+    <hyperlink ref="M98" r:id="rId194" location="region=M100000US390916674099999"/>
+    <hyperlink ref="H99" r:id="rId195"/>
+    <hyperlink ref="M99" r:id="rId196" location="region=M100000US390916913499999"/>
+    <hyperlink ref="H100" r:id="rId197"/>
+    <hyperlink ref="M100" r:id="rId198" location="region=M100000US390917478099999"/>
+    <hyperlink ref="H101" r:id="rId199"/>
+    <hyperlink ref="M101" r:id="rId200" location="region=M100000US390918142499999"/>
+    <hyperlink ref="H102" r:id="rId201"/>
+    <hyperlink ref="M102" r:id="rId202" location="region=M100000US390971123499999"/>
+    <hyperlink ref="H103" r:id="rId203"/>
+    <hyperlink ref="M103" r:id="rId204" location="region=M100000US390972014299999"/>
+    <hyperlink ref="H104" r:id="rId205"/>
+    <hyperlink ref="M104" r:id="rId206" location="region=M100000US390973869699999"/>
+    <hyperlink ref="H105" r:id="rId207"/>
+    <hyperlink ref="M105" r:id="rId208" location="region=M100000US390976333899999"/>
+    <hyperlink ref="H106" r:id="rId209"/>
+    <hyperlink ref="M106" r:id="rId210" location="region=M100000US390977296099999"/>
+    <hyperlink ref="H107" r:id="rId211"/>
+    <hyperlink ref="M107" r:id="rId212" location="region=M100000US390977842899999"/>
+    <hyperlink ref="H108" r:id="rId213"/>
+    <hyperlink ref="M108" r:id="rId214" location="region=M100000US3909890"/>
+    <hyperlink ref="H109" r:id="rId215"/>
+    <hyperlink ref="M109" r:id="rId216" location="region=M100000US391011519699999"/>
+    <hyperlink ref="H110" r:id="rId217"/>
+    <hyperlink ref="M110" r:id="rId218" location="region=M100000US391014776899999"/>
+    <hyperlink ref="H111" r:id="rId219"/>
+    <hyperlink ref="M111" r:id="rId220" location="region=M100000US391015173099999"/>
+    <hyperlink ref="H112" r:id="rId221"/>
+    <hyperlink ref="M112" r:id="rId222" location="region=M100000US391016335299999"/>
+    <hyperlink ref="H113" r:id="rId223"/>
+    <hyperlink ref="M113" r:id="rId224" location="region=M100000US391016479499999"/>
+    <hyperlink ref="H114" r:id="rId225"/>
+    <hyperlink ref="M114" r:id="rId226" location="region=M100000US3911332"/>
+    <hyperlink ref="H115" r:id="rId227"/>
+    <hyperlink ref="M115" r:id="rId228" location="region=M100000US391170550899999"/>
+    <hyperlink ref="H116" r:id="rId229"/>
+    <hyperlink ref="M116" r:id="rId230" location="region=M100000US391171209899999"/>
+    <hyperlink ref="H117" r:id="rId231"/>
+    <hyperlink ref="M117" r:id="rId232" location="region=M100000US391171403099999"/>
+    <hyperlink ref="H118" r:id="rId233"/>
+    <hyperlink ref="M118" r:id="rId234" location="region=M100000US391171829499999"/>
+    <hyperlink ref="H119" r:id="rId235"/>
+    <hyperlink ref="M119" r:id="rId236" location="region=M100000US391173012899999"/>
+    <hyperlink ref="H120" r:id="rId237"/>
+    <hyperlink ref="M120" r:id="rId238" location="region=M100000US391173360099999"/>
+    <hyperlink ref="H121" r:id="rId239"/>
+    <hyperlink ref="M121" r:id="rId240" location="region=M100000US391174368099999"/>
+    <hyperlink ref="H122" r:id="rId241"/>
+    <hyperlink ref="M122" r:id="rId242" location="region=M100000US391176198099999"/>
+    <hyperlink ref="H123" r:id="rId243"/>
+    <hyperlink ref="M123" r:id="rId244" location="region=M100000US3912084"/>
+    <hyperlink ref="H124" r:id="rId245"/>
+    <hyperlink ref="M124" r:id="rId246" location="region=M100000US391273396499999"/>
+    <hyperlink ref="H125" r:id="rId247"/>
+    <hyperlink ref="M125" r:id="rId248" location="region=M100000US391273796899999"/>
+    <hyperlink ref="H126" r:id="rId249"/>
+    <hyperlink ref="M126" r:id="rId250" location="region=M100000US391276268099999"/>
+    <hyperlink ref="H127" r:id="rId251"/>
+    <hyperlink ref="M127" r:id="rId252" location="region=M100000US391276576099999"/>
+    <hyperlink ref="H128" r:id="rId253"/>
+    <hyperlink ref="M128" r:id="rId254" location="region=M100000US391291507799999"/>
+    <hyperlink ref="H129" r:id="rId255"/>
+    <hyperlink ref="M129" r:id="rId256" location="region=M100000US391292015699999"/>
+    <hyperlink ref="H130" r:id="rId257"/>
+    <hyperlink ref="M130" r:id="rId258" location="region=M100000US391293397899999"/>
+    <hyperlink ref="H131" r:id="rId259"/>
+    <hyperlink ref="M131" r:id="rId260" location="region=M100000US391296248499999"/>
+    <hyperlink ref="H132" r:id="rId261"/>
+    <hyperlink ref="M132" r:id="rId262" location="region=M100000US391297018499999"/>
+    <hyperlink ref="H133" r:id="rId263"/>
+    <hyperlink ref="M133" r:id="rId264" location="region=M100000US391297087099999"/>
+    <hyperlink ref="H134" r:id="rId265"/>
+    <hyperlink ref="M134" r:id="rId266" location="region=M100000US391298059899999"/>
+    <hyperlink ref="H135" r:id="rId267"/>
+    <hyperlink ref="M135" r:id="rId268" location="region=M100000US391298155099999"/>
+    <hyperlink ref="H136" r:id="rId269"/>
+    <hyperlink ref="M136" r:id="rId270" location="region=M100000US391411001699999"/>
+    <hyperlink ref="H137" r:id="rId271"/>
+    <hyperlink ref="M137" r:id="rId272" location="region=M100000US391411823899999"/>
+    <hyperlink ref="H138" r:id="rId273"/>
+    <hyperlink ref="M138" r:id="rId274" location="region=M100000US391413689099999"/>
+    <hyperlink ref="H139" r:id="rId275"/>
+    <hyperlink ref="M139" r:id="rId276" location="region=M100000US391414330299999"/>
+    <hyperlink ref="H140" r:id="rId277"/>
+    <hyperlink ref="M140" r:id="rId278" location="region=M100000US391416130899999"/>
+    <hyperlink ref="H141" r:id="rId279"/>
+    <hyperlink ref="M141" r:id="rId280" location="region=M100000US391417089899999"/>
+    <hyperlink ref="H142" r:id="rId281"/>
+    <hyperlink ref="M142" r:id="rId282" location="region=M100000US391417412999999"/>
+    <hyperlink ref="H143" r:id="rId283"/>
+    <hyperlink ref="M143" r:id="rId284" location="region=M100000US391417800899999"/>
+    <hyperlink ref="H144" r:id="rId285"/>
+    <hyperlink ref="M144" r:id="rId286" location="region=M100000US3914184"/>
+    <hyperlink ref="H145" r:id="rId287"/>
+    <hyperlink ref="M145" r:id="rId288" location="region=M100000US3915070"/>
+    <hyperlink ref="H146" r:id="rId289"/>
+    <hyperlink ref="M146" r:id="rId290" location="region=M100000US391590133699999"/>
+    <hyperlink ref="H147" r:id="rId291"/>
+    <hyperlink ref="M147" r:id="rId292" location="region=M100000US391591511299999"/>
+    <hyperlink ref="H148" r:id="rId293"/>
+    <hyperlink ref="M148" r:id="rId294" location="region=M100000US391592017099999"/>
+    <hyperlink ref="H149" r:id="rId295"/>
+    <hyperlink ref="M149" r:id="rId296" location="region=M100000US391592248499999"/>
+    <hyperlink ref="H150" r:id="rId297"/>
+    <hyperlink ref="M150" r:id="rId298" location="region=M100000US391593904699999"/>
+    <hyperlink ref="H151" r:id="rId299"/>
+    <hyperlink ref="M151" r:id="rId300" location="region=M100000US391594335899999"/>
+    <hyperlink ref="H152" r:id="rId301"/>
+    <hyperlink ref="M152" r:id="rId302" location="region=M100000US391595986499999"/>
+    <hyperlink ref="H153" r:id="rId303"/>
+    <hyperlink ref="M153" r:id="rId304" location="region=M100000US3918000"/>
+    <hyperlink ref="H154" r:id="rId305"/>
+    <hyperlink ref="M154" r:id="rId306" location="region=M100000US3918070"/>
+    <hyperlink ref="H155" r:id="rId307"/>
+    <hyperlink ref="M155" r:id="rId308" location="region=M100000US3919456"/>
+    <hyperlink ref="H156" r:id="rId309"/>
+    <hyperlink ref="M156" r:id="rId310" location="region=M100000US3921434"/>
+    <hyperlink ref="H157" r:id="rId311"/>
+    <hyperlink ref="M157" r:id="rId312" location="region=M100000US3922694"/>
+    <hyperlink ref="H158" r:id="rId313"/>
+    <hyperlink ref="M158" r:id="rId314" location="region=M100000US3928658"/>
+    <hyperlink ref="H159" r:id="rId315"/>
+    <hyperlink ref="M159" r:id="rId316" location="region=M100000US3929106"/>
+    <hyperlink ref="H160" r:id="rId317"/>
+    <hyperlink ref="M160" r:id="rId318" location="region=M100000US3929246"/>
+    <hyperlink ref="H161" r:id="rId319"/>
+    <hyperlink ref="M161" r:id="rId320" location="region=M100000US3931304"/>
+    <hyperlink ref="H162" r:id="rId321"/>
+    <hyperlink ref="M162" r:id="rId322" location="region=M100000US3931402"/>
+    <hyperlink ref="H163" r:id="rId323"/>
+    <hyperlink ref="M163" r:id="rId324" location="region=M100000US3932592"/>
+    <hyperlink ref="H164" r:id="rId325"/>
+    <hyperlink ref="M164" r:id="rId326" location="region=M100000US3932606"/>
+    <hyperlink ref="H165" r:id="rId327"/>
+    <hyperlink ref="M165" r:id="rId328" location="region=M100000US3934748"/>
+    <hyperlink ref="H166" r:id="rId329"/>
+    <hyperlink ref="M166" r:id="rId330" location="region=M100000US3934790"/>
+    <hyperlink ref="H167" r:id="rId331"/>
+    <hyperlink ref="M167" r:id="rId332" location="region=M100000US3935476"/>
+    <hyperlink ref="H168" r:id="rId333"/>
+    <hyperlink ref="M168" r:id="rId334" location="region=M100000US3939340"/>
+    <hyperlink ref="H169" r:id="rId335"/>
+    <hyperlink ref="M169" r:id="rId336" location="region=M100000US3941720"/>
+    <hyperlink ref="H170" r:id="rId337"/>
+    <hyperlink ref="M170" r:id="rId338" location="region=M100000US3944086"/>
+    <hyperlink ref="H171" r:id="rId339"/>
+    <hyperlink ref="M171" r:id="rId340" location="region=M100000US3944632"/>
+    <hyperlink ref="H172" r:id="rId341"/>
+    <hyperlink ref="M172" r:id="rId342" location="region=M100000US3944674"/>
+    <hyperlink ref="H173" r:id="rId343"/>
+    <hyperlink ref="M173" r:id="rId344" location="region=M100000US3947754"/>
+    <hyperlink ref="H174" r:id="rId345"/>
+    <hyperlink ref="M174" r:id="rId346" location="region=M100000US3948160"/>
+    <hyperlink ref="H175" r:id="rId347"/>
+    <hyperlink ref="M175" r:id="rId348" location="region=M100000US3950862"/>
+    <hyperlink ref="H176" r:id="rId349"/>
+    <hyperlink ref="M176" r:id="rId350" location="region=M100000US3952738"/>
+    <hyperlink ref="H177" r:id="rId351"/>
+    <hyperlink ref="M177" r:id="rId352" location="region=M100000US3953046"/>
+    <hyperlink ref="H178" r:id="rId353"/>
+    <hyperlink ref="M178" r:id="rId354" location="region=M100000US3953102"/>
+    <hyperlink ref="H179" r:id="rId355"/>
+    <hyperlink ref="M179" r:id="rId356" location="region=M100000US3953970"/>
+    <hyperlink ref="H180" r:id="rId357"/>
+    <hyperlink ref="M180" r:id="rId358" location="region=M100000US3954040"/>
+    <hyperlink ref="H181" r:id="rId359"/>
+    <hyperlink ref="M181" r:id="rId360" location="region=M100000US3954866"/>
+    <hyperlink ref="H182" r:id="rId361"/>
+    <hyperlink ref="M182" r:id="rId362" location="region=M100000US3957862"/>
+    <hyperlink ref="H183" r:id="rId363"/>
+    <hyperlink ref="M183" r:id="rId364" location="region=M100000US3961112"/>
+    <hyperlink ref="H184" r:id="rId365"/>
+    <hyperlink ref="M184" r:id="rId366" location="region=M100000US3962498"/>
+    <hyperlink ref="H185" r:id="rId367"/>
+    <hyperlink ref="M185" r:id="rId368" location="region=M100000US3963030"/>
+    <hyperlink ref="H186" r:id="rId369"/>
+    <hyperlink ref="M186" r:id="rId370" location="region=M100000US3964486"/>
+    <hyperlink ref="H187" r:id="rId371"/>
+    <hyperlink ref="M187" r:id="rId372" location="region=M100000US3966390"/>
+    <hyperlink ref="H188" r:id="rId373"/>
+    <hyperlink ref="M188" r:id="rId374" location="region=M100000US3966936"/>
+    <hyperlink ref="H189" r:id="rId375"/>
+    <hyperlink ref="M189" r:id="rId376" location="region=M100000US3973068"/>
+    <hyperlink ref="H190" r:id="rId377"/>
+    <hyperlink ref="M190" r:id="rId378" location="region=M100000US3975602"/>
+    <hyperlink ref="H191" r:id="rId379"/>
+    <hyperlink ref="M191" r:id="rId380" location="region=M100000US3979002"/>
+    <hyperlink ref="H192" r:id="rId381"/>
+    <hyperlink ref="M192" r:id="rId382" location="region=M100000US3979114"/>
+    <hyperlink ref="H193" r:id="rId383"/>
+    <hyperlink ref="M193" r:id="rId384" location="region=M100000US3981718"/>
+    <hyperlink ref="H194" r:id="rId385"/>
+    <hyperlink ref="M194" r:id="rId386" location="region=M100000US3983342"/>
+    <hyperlink ref="H195" r:id="rId387"/>
+    <hyperlink ref="M195" r:id="rId388" location="region=M100000US3983580"/>
+    <hyperlink ref="H196" r:id="rId389"/>
+    <hyperlink ref="M196" r:id="rId390" location="region=M100000US3984742"/>
+    <hyperlink ref="H197" r:id="rId391"/>
+    <hyperlink ref="M197" r:id="rId392" location="region=M100000US3986604"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
